--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED465A7-7FC3-49C9-9436-67986F33AF3B}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56097DFB-04DF-453D-B8BD-DE78E0E622F4}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>oil_price</t>
   </si>
@@ -43,33 +42,6 @@
   </si>
   <si>
     <t>gas_price</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>WTI</t>
-  </si>
-  <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>SourceWTI</t>
-  </si>
-  <si>
-    <t>SourceHH</t>
-  </si>
-  <si>
-    <t>MaxAsOfDate</t>
-  </si>
-  <si>
-    <t>SETTLED</t>
-  </si>
-  <si>
-    <t>AVG</t>
-  </si>
-  <si>
-    <t>STRIP</t>
   </si>
 </sst>
 </file>
@@ -107,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -122,7 +94,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +558,7 @@
         <v>82.451999999999998</v>
       </c>
       <c r="C9">
-        <v>2.9213499999999999</v>
+        <v>2.7410000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -595,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>89.513999999999996</v>
+        <v>97.533000000000001</v>
       </c>
       <c r="C10">
-        <v>2.9213499999999999</v>
+        <v>2.8184999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -606,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>86.739000000000004</v>
+        <v>95.489000000000004</v>
       </c>
       <c r="C11">
-        <v>2.9039999999999999</v>
+        <v>2.8959999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>84.328000000000003</v>
+        <v>91.613</v>
       </c>
       <c r="C12">
-        <v>3.0339999999999998</v>
+        <v>3.0459999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>81.686999999999998</v>
+        <v>87.619</v>
       </c>
       <c r="C13">
-        <v>3.4929999999999999</v>
+        <v>3.4769999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>79.489000000000004</v>
+        <v>84.462999999999994</v>
       </c>
       <c r="C14">
-        <v>3.9159999999999999</v>
+        <v>3.875</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>78.034999999999997</v>
+        <v>82.379000000000005</v>
       </c>
       <c r="C15">
-        <v>3.5739999999999998</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>76.573999999999998</v>
+        <v>80.143000000000001</v>
       </c>
       <c r="C16">
-        <v>2.9009999999999998</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>75.399000000000001</v>
+        <v>78.215000000000003</v>
       </c>
       <c r="C17">
-        <v>2.77</v>
+        <v>2.7610000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>74.591999999999999</v>
+        <v>76.813999999999993</v>
       </c>
       <c r="C18">
-        <v>2.7850000000000001</v>
+        <v>2.7789999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,7 +665,7 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>73.869</v>
+        <v>75.578999999999994</v>
       </c>
       <c r="C19">
         <v>2.9289999999999998</v>
@@ -705,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>73.180000000000007</v>
+        <v>74.465000000000003</v>
       </c>
       <c r="C20">
-        <v>3.141</v>
+        <v>3.1440000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>72.683999999999997</v>
+        <v>73.697000000000003</v>
       </c>
       <c r="C21">
-        <v>3.2149999999999999</v>
+        <v>3.2189999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>72.212999999999994</v>
+        <v>73.037000000000006</v>
       </c>
       <c r="C22">
-        <v>3.2</v>
+        <v>3.2040000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>71.816999999999993</v>
+        <v>72.513000000000005</v>
       </c>
       <c r="C23">
-        <v>3.2829999999999999</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>71.460999999999999</v>
+        <v>72.070999999999998</v>
       </c>
       <c r="C24">
-        <v>3.5449999999999999</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.058999999999997</v>
+        <v>71.600999999999999</v>
       </c>
       <c r="C25">
-        <v>4.1660000000000004</v>
+        <v>4.2080000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>70.715000000000003</v>
+        <v>71.210999999999999</v>
       </c>
       <c r="C26">
-        <v>4.6109999999999998</v>
+        <v>4.6520000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.424999999999997</v>
+        <v>70.888000000000005</v>
       </c>
       <c r="C27">
-        <v>4.1829999999999998</v>
+        <v>4.2300000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -793,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.113</v>
+        <v>70.539000000000001</v>
       </c>
       <c r="C28">
-        <v>3.4220000000000002</v>
+        <v>3.4860000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>69.876999999999995</v>
+        <v>70.265000000000001</v>
       </c>
       <c r="C29">
-        <v>3.1709999999999998</v>
+        <v>3.2320000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -815,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>69.652000000000001</v>
+        <v>69.998000000000005</v>
       </c>
       <c r="C30">
-        <v>3.16</v>
+        <v>3.226</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.375</v>
+        <v>69.665999999999997</v>
       </c>
       <c r="C31">
-        <v>3.3119999999999998</v>
+        <v>3.383</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.14</v>
+        <v>69.382000000000005</v>
       </c>
       <c r="C32">
-        <v>3.5139999999999998</v>
+        <v>3.585</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>68.926000000000002</v>
+        <v>69.117999999999995</v>
       </c>
       <c r="C33">
-        <v>3.5760000000000001</v>
+        <v>3.6480000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -859,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.716999999999999</v>
+        <v>68.846000000000004</v>
       </c>
       <c r="C34">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.543000000000006</v>
+        <v>68.614000000000004</v>
       </c>
       <c r="C35">
-        <v>3.601</v>
+        <v>3.6680000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -881,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.346999999999994</v>
+        <v>68.36</v>
       </c>
       <c r="C36">
-        <v>3.7519999999999998</v>
+        <v>3.8330000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.123000000000005</v>
+        <v>68.088999999999999</v>
       </c>
       <c r="C37">
-        <v>4.3170000000000002</v>
+        <v>4.3840000000000003</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.917000000000002</v>
+        <v>67.837000000000003</v>
       </c>
       <c r="C38">
-        <v>4.7640000000000002</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.733000000000004</v>
+        <v>67.596999999999994</v>
       </c>
       <c r="C39">
-        <v>4.33</v>
+        <v>4.343</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.552999999999997</v>
+        <v>67.367000000000004</v>
       </c>
       <c r="C40">
-        <v>3.4470000000000001</v>
+        <v>3.4369999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.394000000000005</v>
+        <v>67.150999999999996</v>
       </c>
       <c r="C41">
-        <v>3.1619999999999999</v>
+        <v>3.161</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,7 +918,7 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.224999999999994</v>
+        <v>66.906000000000006</v>
       </c>
       <c r="C42">
         <v>3.1440000000000001</v>
@@ -958,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.013999999999996</v>
+        <v>66.623000000000005</v>
       </c>
       <c r="C43">
-        <v>3.2690000000000001</v>
+        <v>3.2730000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.83</v>
+        <v>66.39</v>
       </c>
       <c r="C44">
-        <v>3.472</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.653999999999996</v>
+        <v>66.177000000000007</v>
       </c>
       <c r="C45">
-        <v>3.5350000000000001</v>
+        <v>3.5430000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -991,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.503</v>
+        <v>65.974000000000004</v>
       </c>
       <c r="C46">
-        <v>3.52</v>
+        <v>3.5259999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1002,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.353999999999999</v>
+        <v>65.766000000000005</v>
       </c>
       <c r="C47">
-        <v>3.5760000000000001</v>
+        <v>3.5819999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.174000000000007</v>
+        <v>65.525000000000006</v>
       </c>
       <c r="C48">
-        <v>3.7269999999999999</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.977000000000004</v>
+        <v>65.275999999999996</v>
       </c>
       <c r="C49">
-        <v>4.2869999999999999</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,7 +1006,7 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.787000000000006</v>
+        <v>65.027000000000001</v>
       </c>
       <c r="C50">
         <v>4.7480000000000002</v>
@@ -1046,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.635999999999996</v>
+        <v>64.816999999999993</v>
       </c>
       <c r="C51">
-        <v>4.3239999999999998</v>
+        <v>4.3440000000000003</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.492999999999995</v>
+        <v>64.62</v>
       </c>
       <c r="C52">
-        <v>3.4790000000000001</v>
+        <v>3.4980000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.349000000000004</v>
+        <v>64.436999999999998</v>
       </c>
       <c r="C53">
-        <v>3.1019999999999999</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.156000000000006</v>
+        <v>64.2</v>
       </c>
       <c r="C54">
-        <v>3.0579999999999998</v>
+        <v>3.1070000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1090,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.968999999999994</v>
+        <v>63.963999999999999</v>
       </c>
       <c r="C55">
-        <v>3.173</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.808999999999997</v>
+        <v>63.76</v>
       </c>
       <c r="C56">
-        <v>3.407</v>
+        <v>3.4529999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.644999999999996</v>
+        <v>63.567999999999998</v>
       </c>
       <c r="C57">
-        <v>3.4510000000000001</v>
+        <v>3.4910000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1434,1270 +1405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181BEF81-CE8F-4D5A-B9EC-49C0C8B5AE38}">
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B2">
-        <v>63.533999999999999</v>
-      </c>
-      <c r="C2">
-        <v>2.9498000000000002</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B3">
-        <v>60.07</v>
-      </c>
-      <c r="C3">
-        <v>3.1211000000000002</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>45962</v>
-      </c>
-      <c r="B4">
-        <v>59.478999999999999</v>
-      </c>
-      <c r="C4">
-        <v>3.7837999999999998</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>45992</v>
-      </c>
-      <c r="B5">
-        <v>57.866</v>
-      </c>
-      <c r="C5">
-        <v>4.1501999999999999</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B6">
-        <v>60.26</v>
-      </c>
-      <c r="C6">
-        <v>7.7126000000000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B7">
-        <v>64.522999999999996</v>
-      </c>
-      <c r="C7">
-        <v>3.8382000000000001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46082</v>
-      </c>
-      <c r="B8">
-        <v>90.997</v>
-      </c>
-      <c r="C8">
-        <v>3.0581999999999998</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B9">
-        <v>98.06</v>
-      </c>
-      <c r="C9">
-        <v>2.7736999999999998</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B10">
-        <v>98.513999999999996</v>
-      </c>
-      <c r="C10">
-        <v>2.8881999999999999</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B11">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="C11">
-        <v>3.1429999999999998</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>46204</v>
-      </c>
-      <c r="B12">
-        <v>79.22</v>
-      </c>
-      <c r="C12">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B13">
-        <v>82.451999999999998</v>
-      </c>
-      <c r="C13">
-        <v>2.9213499999999999</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>46266</v>
-      </c>
-      <c r="B14">
-        <v>89.513999999999996</v>
-      </c>
-      <c r="C14">
-        <v>2.9213499999999999</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46296</v>
-      </c>
-      <c r="B15">
-        <v>86.739000000000004</v>
-      </c>
-      <c r="C15">
-        <v>2.9039999999999999</v>
-      </c>
-      <c r="D15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>46327</v>
-      </c>
-      <c r="B16">
-        <v>84.328000000000003</v>
-      </c>
-      <c r="C16">
-        <v>3.0339999999999998</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>46357</v>
-      </c>
-      <c r="B17">
-        <v>81.686999999999998</v>
-      </c>
-      <c r="C17">
-        <v>3.4929999999999999</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>46388</v>
-      </c>
-      <c r="B18">
-        <v>79.489000000000004</v>
-      </c>
-      <c r="C18">
-        <v>3.9159999999999999</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>46419</v>
-      </c>
-      <c r="B19">
-        <v>78.034999999999997</v>
-      </c>
-      <c r="C19">
-        <v>3.5739999999999998</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46447</v>
-      </c>
-      <c r="B20">
-        <v>76.573999999999998</v>
-      </c>
-      <c r="C20">
-        <v>2.9009999999999998</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>46478</v>
-      </c>
-      <c r="B21">
-        <v>75.399000000000001</v>
-      </c>
-      <c r="C21">
-        <v>2.77</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>46508</v>
-      </c>
-      <c r="B22">
-        <v>74.591999999999999</v>
-      </c>
-      <c r="C22">
-        <v>2.7850000000000001</v>
-      </c>
-      <c r="D22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>46539</v>
-      </c>
-      <c r="B23">
-        <v>73.869</v>
-      </c>
-      <c r="C23">
-        <v>2.9289999999999998</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46569</v>
-      </c>
-      <c r="B24">
-        <v>73.180000000000007</v>
-      </c>
-      <c r="C24">
-        <v>3.141</v>
-      </c>
-      <c r="D24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>46600</v>
-      </c>
-      <c r="B25">
-        <v>72.683999999999997</v>
-      </c>
-      <c r="C25">
-        <v>3.2149999999999999</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>46631</v>
-      </c>
-      <c r="B26">
-        <v>72.212999999999994</v>
-      </c>
-      <c r="C26">
-        <v>3.2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>46661</v>
-      </c>
-      <c r="B27">
-        <v>71.816999999999993</v>
-      </c>
-      <c r="C27">
-        <v>3.2829999999999999</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>46692</v>
-      </c>
-      <c r="B28">
-        <v>71.460999999999999</v>
-      </c>
-      <c r="C28">
-        <v>3.5449999999999999</v>
-      </c>
-      <c r="D28" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>46722</v>
-      </c>
-      <c r="B29">
-        <v>71.058999999999997</v>
-      </c>
-      <c r="C29">
-        <v>4.1660000000000004</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>46753</v>
-      </c>
-      <c r="B30">
-        <v>70.715000000000003</v>
-      </c>
-      <c r="C30">
-        <v>4.6109999999999998</v>
-      </c>
-      <c r="D30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>46784</v>
-      </c>
-      <c r="B31">
-        <v>70.424999999999997</v>
-      </c>
-      <c r="C31">
-        <v>4.1829999999999998</v>
-      </c>
-      <c r="D31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>46813</v>
-      </c>
-      <c r="B32">
-        <v>70.113</v>
-      </c>
-      <c r="C32">
-        <v>3.4220000000000002</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>46844</v>
-      </c>
-      <c r="B33">
-        <v>69.876999999999995</v>
-      </c>
-      <c r="C33">
-        <v>3.1709999999999998</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>46874</v>
-      </c>
-      <c r="B34">
-        <v>69.652000000000001</v>
-      </c>
-      <c r="C34">
-        <v>3.16</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>46905</v>
-      </c>
-      <c r="B35">
-        <v>69.375</v>
-      </c>
-      <c r="C35">
-        <v>3.3119999999999998</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>46935</v>
-      </c>
-      <c r="B36">
-        <v>69.14</v>
-      </c>
-      <c r="C36">
-        <v>3.5139999999999998</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" t="s">
-        <v>11</v>
-      </c>
-      <c r="F36" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>46966</v>
-      </c>
-      <c r="B37">
-        <v>68.926000000000002</v>
-      </c>
-      <c r="C37">
-        <v>3.5760000000000001</v>
-      </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>11</v>
-      </c>
-      <c r="F37" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>46997</v>
-      </c>
-      <c r="B38">
-        <v>68.716999999999999</v>
-      </c>
-      <c r="C38">
-        <v>3.55</v>
-      </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>47027</v>
-      </c>
-      <c r="B39">
-        <v>68.543000000000006</v>
-      </c>
-      <c r="C39">
-        <v>3.601</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>47058</v>
-      </c>
-      <c r="B40">
-        <v>68.346999999999994</v>
-      </c>
-      <c r="C40">
-        <v>3.7519999999999998</v>
-      </c>
-      <c r="D40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>47088</v>
-      </c>
-      <c r="B41">
-        <v>68.123000000000005</v>
-      </c>
-      <c r="C41">
-        <v>4.3170000000000002</v>
-      </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>47119</v>
-      </c>
-      <c r="B42">
-        <v>67.917000000000002</v>
-      </c>
-      <c r="C42">
-        <v>4.7640000000000002</v>
-      </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>47150</v>
-      </c>
-      <c r="B43">
-        <v>67.733000000000004</v>
-      </c>
-      <c r="C43">
-        <v>4.33</v>
-      </c>
-      <c r="D43" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>47178</v>
-      </c>
-      <c r="B44">
-        <v>67.552999999999997</v>
-      </c>
-      <c r="C44">
-        <v>3.4470000000000001</v>
-      </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>47209</v>
-      </c>
-      <c r="B45">
-        <v>67.394000000000005</v>
-      </c>
-      <c r="C45">
-        <v>3.1619999999999999</v>
-      </c>
-      <c r="D45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>47239</v>
-      </c>
-      <c r="B46">
-        <v>67.224999999999994</v>
-      </c>
-      <c r="C46">
-        <v>3.1440000000000001</v>
-      </c>
-      <c r="D46" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>47270</v>
-      </c>
-      <c r="B47">
-        <v>67.013999999999996</v>
-      </c>
-      <c r="C47">
-        <v>3.2690000000000001</v>
-      </c>
-      <c r="D47" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>47300</v>
-      </c>
-      <c r="B48">
-        <v>66.83</v>
-      </c>
-      <c r="C48">
-        <v>3.472</v>
-      </c>
-      <c r="D48" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>47331</v>
-      </c>
-      <c r="B49">
-        <v>66.653999999999996</v>
-      </c>
-      <c r="C49">
-        <v>3.5350000000000001</v>
-      </c>
-      <c r="D49" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>47362</v>
-      </c>
-      <c r="B50">
-        <v>66.503</v>
-      </c>
-      <c r="C50">
-        <v>3.52</v>
-      </c>
-      <c r="D50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>47392</v>
-      </c>
-      <c r="B51">
-        <v>66.353999999999999</v>
-      </c>
-      <c r="C51">
-        <v>3.5760000000000001</v>
-      </c>
-      <c r="D51" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>47423</v>
-      </c>
-      <c r="B52">
-        <v>66.174000000000007</v>
-      </c>
-      <c r="C52">
-        <v>3.7269999999999999</v>
-      </c>
-      <c r="D52" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>47453</v>
-      </c>
-      <c r="B53">
-        <v>65.977000000000004</v>
-      </c>
-      <c r="C53">
-        <v>4.2869999999999999</v>
-      </c>
-      <c r="D53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>47484</v>
-      </c>
-      <c r="B54">
-        <v>65.787000000000006</v>
-      </c>
-      <c r="C54">
-        <v>4.7480000000000002</v>
-      </c>
-      <c r="D54" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>47515</v>
-      </c>
-      <c r="B55">
-        <v>65.635999999999996</v>
-      </c>
-      <c r="C55">
-        <v>4.3239999999999998</v>
-      </c>
-      <c r="D55" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>47543</v>
-      </c>
-      <c r="B56">
-        <v>65.492999999999995</v>
-      </c>
-      <c r="C56">
-        <v>3.4790000000000001</v>
-      </c>
-      <c r="D56" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>47574</v>
-      </c>
-      <c r="B57">
-        <v>65.349000000000004</v>
-      </c>
-      <c r="C57">
-        <v>3.1019999999999999</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>47604</v>
-      </c>
-      <c r="B58">
-        <v>65.156000000000006</v>
-      </c>
-      <c r="C58">
-        <v>3.0579999999999998</v>
-      </c>
-      <c r="D58" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>47635</v>
-      </c>
-      <c r="B59">
-        <v>64.968999999999994</v>
-      </c>
-      <c r="C59">
-        <v>3.173</v>
-      </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>47665</v>
-      </c>
-      <c r="B60">
-        <v>64.808999999999997</v>
-      </c>
-      <c r="C60">
-        <v>3.407</v>
-      </c>
-      <c r="D60" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>47696</v>
-      </c>
-      <c r="B61">
-        <v>64.644999999999996</v>
-      </c>
-      <c r="C61">
-        <v>3.4510000000000001</v>
-      </c>
-      <c r="D61" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="6">
-        <v>46266</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -2992,7 +1700,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3001,18 +1709,40 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3031,10 +1761,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56097DFB-04DF-453D-B8BD-DE78E0E622F4}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43A43F6-A1E5-4595-B33F-86AB5C075B2B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>97.533000000000001</v>
+        <v>99.832999999999998</v>
       </c>
       <c r="C10">
-        <v>2.8184999999999998</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>95.489000000000004</v>
+        <v>98.844999999999999</v>
       </c>
       <c r="C11">
-        <v>2.8959999999999999</v>
+        <v>2.919</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>91.613</v>
+        <v>94.388000000000005</v>
       </c>
       <c r="C12">
-        <v>3.0459999999999998</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>87.619</v>
+        <v>89.855000000000004</v>
       </c>
       <c r="C13">
-        <v>3.4769999999999999</v>
+        <v>3.464</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>84.462999999999994</v>
+        <v>86.31</v>
       </c>
       <c r="C14">
-        <v>3.875</v>
+        <v>3.851</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>82.379000000000005</v>
+        <v>84.009</v>
       </c>
       <c r="C15">
-        <v>3.5369999999999999</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>80.143000000000001</v>
+        <v>81.578999999999994</v>
       </c>
       <c r="C16">
-        <v>2.891</v>
+        <v>2.8809999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>78.215000000000003</v>
+        <v>79.492000000000004</v>
       </c>
       <c r="C17">
-        <v>2.7610000000000001</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>76.813999999999993</v>
+        <v>77.971999999999994</v>
       </c>
       <c r="C18">
-        <v>2.7789999999999999</v>
+        <v>2.782</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>75.578999999999994</v>
+        <v>76.599000000000004</v>
       </c>
       <c r="C19">
-        <v>2.9289999999999998</v>
+        <v>2.9329999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>74.465000000000003</v>
+        <v>75.334999999999994</v>
       </c>
       <c r="C20">
-        <v>3.1440000000000001</v>
+        <v>3.1480000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>73.697000000000003</v>
+        <v>74.445999999999998</v>
       </c>
       <c r="C21">
-        <v>3.2189999999999999</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>73.037000000000006</v>
+        <v>73.653000000000006</v>
       </c>
       <c r="C22">
-        <v>3.2040000000000002</v>
+        <v>3.2069999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.513000000000005</v>
+        <v>73.007000000000005</v>
       </c>
       <c r="C23">
-        <v>3.29</v>
+        <v>3.2930000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>72.070999999999998</v>
+        <v>72.465999999999994</v>
       </c>
       <c r="C24">
-        <v>3.58</v>
+        <v>3.5880000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.600999999999999</v>
+        <v>71.902000000000001</v>
       </c>
       <c r="C25">
-        <v>4.2080000000000002</v>
+        <v>4.2190000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.210999999999999</v>
+        <v>71.442999999999998</v>
       </c>
       <c r="C26">
-        <v>4.6520000000000001</v>
+        <v>4.6529999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>70.888000000000005</v>
+        <v>71.075000000000003</v>
       </c>
       <c r="C27">
-        <v>4.2300000000000004</v>
+        <v>4.2270000000000003</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.539000000000001</v>
+        <v>70.668000000000006</v>
       </c>
       <c r="C28">
-        <v>3.4860000000000002</v>
+        <v>3.4889999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.265000000000001</v>
+        <v>70.338999999999999</v>
       </c>
       <c r="C29">
-        <v>3.2320000000000002</v>
+        <v>3.2410000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>69.998000000000005</v>
+        <v>70.027000000000001</v>
       </c>
       <c r="C30">
-        <v>3.226</v>
+        <v>3.2349999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.665999999999997</v>
+        <v>69.650000000000006</v>
       </c>
       <c r="C31">
-        <v>3.383</v>
+        <v>3.3940000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.382000000000005</v>
+        <v>69.328000000000003</v>
       </c>
       <c r="C32">
-        <v>3.585</v>
+        <v>3.5979999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.117999999999995</v>
+        <v>69.025999999999996</v>
       </c>
       <c r="C33">
-        <v>3.6480000000000001</v>
+        <v>3.6589999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.846000000000004</v>
+        <v>68.715999999999994</v>
       </c>
       <c r="C34">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.614000000000004</v>
+        <v>68.459999999999994</v>
       </c>
       <c r="C35">
-        <v>3.6680000000000001</v>
+        <v>3.6779999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.36</v>
+        <v>68.192999999999998</v>
       </c>
       <c r="C36">
-        <v>3.8330000000000002</v>
+        <v>3.8439999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.088999999999999</v>
+        <v>67.899000000000001</v>
       </c>
       <c r="C37">
-        <v>4.3840000000000003</v>
+        <v>4.391</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.837000000000003</v>
+        <v>67.617000000000004</v>
       </c>
       <c r="C38">
-        <v>4.82</v>
+        <v>4.8250000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.596999999999994</v>
+        <v>67.347999999999999</v>
       </c>
       <c r="C39">
-        <v>4.343</v>
+        <v>4.3529999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.367000000000004</v>
+        <v>67.087000000000003</v>
       </c>
       <c r="C40">
-        <v>3.4369999999999998</v>
+        <v>3.4449999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.150999999999996</v>
+        <v>66.846000000000004</v>
       </c>
       <c r="C41">
-        <v>3.161</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.906000000000006</v>
+        <v>66.581000000000003</v>
       </c>
       <c r="C42">
-        <v>3.1440000000000001</v>
+        <v>3.153</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.623000000000005</v>
+        <v>66.275999999999996</v>
       </c>
       <c r="C43">
-        <v>3.2730000000000001</v>
+        <v>3.2810000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.39</v>
+        <v>66.016999999999996</v>
       </c>
       <c r="C44">
-        <v>3.48</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.177000000000007</v>
+        <v>65.766999999999996</v>
       </c>
       <c r="C45">
-        <v>3.5430000000000001</v>
+        <v>3.5510000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.974000000000004</v>
+        <v>65.540999999999997</v>
       </c>
       <c r="C46">
-        <v>3.5259999999999998</v>
+        <v>3.5329999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.766000000000005</v>
+        <v>65.325999999999993</v>
       </c>
       <c r="C47">
-        <v>3.5819999999999999</v>
+        <v>3.5830000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.525000000000006</v>
+        <v>65.081000000000003</v>
       </c>
       <c r="C48">
         <v>3.72</v>
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.275999999999996</v>
+        <v>64.819000000000003</v>
       </c>
       <c r="C49">
-        <v>4.28</v>
+        <v>4.2779999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,7 +1006,7 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.027000000000001</v>
+        <v>64.552999999999997</v>
       </c>
       <c r="C50">
         <v>4.7480000000000002</v>
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.816999999999993</v>
+        <v>64.334000000000003</v>
       </c>
       <c r="C51">
-        <v>4.3440000000000003</v>
+        <v>4.343</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,7 +1028,7 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.62</v>
+        <v>64.123000000000005</v>
       </c>
       <c r="C52">
         <v>3.4980000000000002</v>
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.436999999999998</v>
+        <v>63.923999999999999</v>
       </c>
       <c r="C53">
-        <v>3.1509999999999998</v>
+        <v>3.1520000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.2</v>
+        <v>63.673999999999999</v>
       </c>
       <c r="C54">
-        <v>3.1070000000000002</v>
+        <v>3.1080000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>63.963999999999999</v>
+        <v>63.420999999999999</v>
       </c>
       <c r="C55">
-        <v>3.22</v>
+        <v>3.2210000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>63.76</v>
+        <v>63.203000000000003</v>
       </c>
       <c r="C56">
-        <v>3.4529999999999998</v>
+        <v>3.4550000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.567999999999998</v>
+        <v>62.991</v>
       </c>
       <c r="C57">
-        <v>3.4910000000000001</v>
+        <v>3.4929999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,6 +1406,48 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1700,49 +1742,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1759,23 +1778,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B43A43F6-A1E5-4595-B33F-86AB5C075B2B}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AECFA37F-B29C-4677-AFB5-F5359A3E6941}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>99.832999999999998</v>
+        <v>98.097999999999999</v>
       </c>
       <c r="C10">
-        <v>2.83</v>
+        <v>2.8159999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>98.844999999999999</v>
+        <v>95.793999999999997</v>
       </c>
       <c r="C11">
-        <v>2.919</v>
+        <v>2.891</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>94.388000000000005</v>
+        <v>91.82</v>
       </c>
       <c r="C12">
-        <v>3.05</v>
+        <v>3.0129999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>89.855000000000004</v>
+        <v>87.891999999999996</v>
       </c>
       <c r="C13">
-        <v>3.464</v>
+        <v>3.4140000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>86.31</v>
+        <v>84.778000000000006</v>
       </c>
       <c r="C14">
-        <v>3.851</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>84.009</v>
+        <v>82.733999999999995</v>
       </c>
       <c r="C15">
-        <v>3.52</v>
+        <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>81.578999999999994</v>
+        <v>80.575000000000003</v>
       </c>
       <c r="C16">
-        <v>2.8809999999999998</v>
+        <v>2.8439999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>79.492000000000004</v>
+        <v>78.734999999999999</v>
       </c>
       <c r="C17">
-        <v>2.76</v>
+        <v>2.734</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>77.971999999999994</v>
+        <v>77.393000000000001</v>
       </c>
       <c r="C18">
-        <v>2.782</v>
+        <v>2.7639999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>76.599000000000004</v>
+        <v>76.176000000000002</v>
       </c>
       <c r="C19">
-        <v>2.9329999999999998</v>
+        <v>2.923</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>75.334999999999994</v>
+        <v>75.040000000000006</v>
       </c>
       <c r="C20">
-        <v>3.1480000000000001</v>
+        <v>3.1419999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>74.445999999999998</v>
+        <v>74.230999999999995</v>
       </c>
       <c r="C21">
-        <v>3.222</v>
+        <v>3.2160000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>73.653000000000006</v>
+        <v>73.513000000000005</v>
       </c>
       <c r="C22">
-        <v>3.2069999999999999</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>73.007000000000005</v>
+        <v>72.917000000000002</v>
       </c>
       <c r="C23">
-        <v>3.2930000000000001</v>
+        <v>3.286</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>72.465999999999994</v>
+        <v>72.403999999999996</v>
       </c>
       <c r="C24">
-        <v>3.5880000000000001</v>
+        <v>3.581</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.902000000000001</v>
+        <v>71.869</v>
       </c>
       <c r="C25">
-        <v>4.2190000000000003</v>
+        <v>4.2060000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.442999999999998</v>
+        <v>71.427000000000007</v>
       </c>
       <c r="C26">
-        <v>4.6529999999999996</v>
+        <v>4.6379999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>71.075000000000003</v>
+        <v>71.064999999999998</v>
       </c>
       <c r="C27">
-        <v>4.2270000000000003</v>
+        <v>4.2169999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.668000000000006</v>
+        <v>70.665000000000006</v>
       </c>
       <c r="C28">
-        <v>3.4889999999999999</v>
+        <v>3.4769999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.338999999999999</v>
+        <v>70.352000000000004</v>
       </c>
       <c r="C29">
-        <v>3.2410000000000001</v>
+        <v>3.2360000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.027000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="C30">
-        <v>3.2349999999999999</v>
+        <v>3.2330000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.650000000000006</v>
+        <v>69.691999999999993</v>
       </c>
       <c r="C31">
-        <v>3.3940000000000001</v>
+        <v>3.395</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.328000000000003</v>
+        <v>69.394999999999996</v>
       </c>
       <c r="C32">
-        <v>3.5979999999999999</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.025999999999996</v>
+        <v>69.111999999999995</v>
       </c>
       <c r="C33">
-        <v>3.6589999999999998</v>
+        <v>3.6619999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.715999999999994</v>
+        <v>68.819000000000003</v>
       </c>
       <c r="C34">
-        <v>3.63</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.459999999999994</v>
+        <v>68.576999999999998</v>
       </c>
       <c r="C35">
-        <v>3.6779999999999999</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.192999999999998</v>
+        <v>68.326999999999998</v>
       </c>
       <c r="C36">
-        <v>3.8439999999999999</v>
+        <v>3.8519999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>67.899000000000001</v>
+        <v>68.039000000000001</v>
       </c>
       <c r="C37">
-        <v>4.391</v>
+        <v>4.3949999999999996</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.617000000000004</v>
+        <v>67.760000000000005</v>
       </c>
       <c r="C38">
-        <v>4.8250000000000002</v>
+        <v>4.827</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.347999999999999</v>
+        <v>67.501000000000005</v>
       </c>
       <c r="C39">
-        <v>4.3529999999999998</v>
+        <v>4.3579999999999997</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.087000000000003</v>
+        <v>67.257000000000005</v>
       </c>
       <c r="C40">
-        <v>3.4449999999999998</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>66.846000000000004</v>
+        <v>67.040999999999997</v>
       </c>
       <c r="C41">
-        <v>3.17</v>
+        <v>3.1749999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.581000000000003</v>
+        <v>66.793999999999997</v>
       </c>
       <c r="C42">
-        <v>3.153</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.275999999999996</v>
+        <v>66.492000000000004</v>
       </c>
       <c r="C43">
-        <v>3.2810000000000001</v>
+        <v>3.286</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.016999999999996</v>
+        <v>66.233000000000004</v>
       </c>
       <c r="C44">
-        <v>3.488</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>65.766999999999996</v>
+        <v>66</v>
       </c>
       <c r="C45">
-        <v>3.5510000000000002</v>
+        <v>3.5550000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.540999999999997</v>
+        <v>65.787000000000006</v>
       </c>
       <c r="C46">
-        <v>3.5329999999999999</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.325999999999993</v>
+        <v>65.588999999999999</v>
       </c>
       <c r="C47">
-        <v>3.5830000000000002</v>
+        <v>3.5880000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.081000000000003</v>
+        <v>65.355000000000004</v>
       </c>
       <c r="C48">
-        <v>3.72</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>64.819000000000003</v>
+        <v>65.102000000000004</v>
       </c>
       <c r="C49">
-        <v>4.2779999999999996</v>
+        <v>4.2789999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>64.552999999999997</v>
+        <v>64.849999999999994</v>
       </c>
       <c r="C50">
-        <v>4.7480000000000002</v>
+        <v>4.7450000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.334000000000003</v>
+        <v>64.647000000000006</v>
       </c>
       <c r="C51">
-        <v>4.343</v>
+        <v>4.3410000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.123000000000005</v>
+        <v>64.447000000000003</v>
       </c>
       <c r="C52">
-        <v>3.4980000000000002</v>
+        <v>3.4910000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>63.923999999999999</v>
+        <v>64.257000000000005</v>
       </c>
       <c r="C53">
-        <v>3.1520000000000001</v>
+        <v>3.1459999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>63.673999999999999</v>
+        <v>64.016999999999996</v>
       </c>
       <c r="C54">
-        <v>3.1080000000000001</v>
+        <v>3.1030000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>63.420999999999999</v>
+        <v>63.771000000000001</v>
       </c>
       <c r="C55">
-        <v>3.2210000000000001</v>
+        <v>3.2170000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>63.203000000000003</v>
+        <v>63.555999999999997</v>
       </c>
       <c r="C56">
-        <v>3.4550000000000001</v>
+        <v>3.4510000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>62.991</v>
+        <v>63.350999999999999</v>
       </c>
       <c r="C57">
-        <v>3.4929999999999999</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,6 +1406,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
@@ -1436,15 +1445,6 @@
     </_ApprovalSentBy>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1743,20 +1743,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
     <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AECFA37F-B29C-4677-AFB5-F5359A3E6941}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBCDA1A9-594A-4E3C-ACDC-F9AB9F0C4CCE}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
   <si>
     <t>oil_price</t>
   </si>
@@ -42,6 +43,33 @@
   </si>
   <si>
     <t>gas_price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>WTI</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>SourceWTI</t>
+  </si>
+  <si>
+    <t>SourceHH</t>
+  </si>
+  <si>
+    <t>MaxAsOfDate</t>
+  </si>
+  <si>
+    <t>SETTLED</t>
+  </si>
+  <si>
+    <t>STRIP</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -79,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -94,6 +122,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,10 +595,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>98.097999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="C10">
-        <v>2.8159999999999998</v>
+        <v>2.8264999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +606,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>95.793999999999997</v>
+        <v>94.614999999999995</v>
       </c>
       <c r="C11">
-        <v>2.891</v>
+        <v>2.9119999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +617,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>91.82</v>
+        <v>91.25</v>
       </c>
       <c r="C12">
-        <v>3.0129999999999999</v>
+        <v>3.0430000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +628,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>87.891999999999996</v>
+        <v>87.974999999999994</v>
       </c>
       <c r="C13">
-        <v>3.4140000000000001</v>
+        <v>3.395</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +639,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>84.778000000000006</v>
+        <v>85.253</v>
       </c>
       <c r="C14">
-        <v>3.8</v>
+        <v>3.7410000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +650,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>82.733999999999995</v>
+        <v>83.382999999999996</v>
       </c>
       <c r="C15">
-        <v>3.4740000000000002</v>
+        <v>3.4390000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +661,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>80.575000000000003</v>
+        <v>81.358999999999995</v>
       </c>
       <c r="C16">
-        <v>2.8439999999999999</v>
+        <v>2.8119999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +672,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>78.734999999999999</v>
+        <v>79.605999999999995</v>
       </c>
       <c r="C17">
-        <v>2.734</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +683,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>77.393000000000001</v>
+        <v>78.314999999999998</v>
       </c>
       <c r="C18">
-        <v>2.7639999999999998</v>
+        <v>2.7450000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +694,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>76.176000000000002</v>
+        <v>77.134</v>
       </c>
       <c r="C19">
-        <v>2.923</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +705,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>75.040000000000006</v>
+        <v>76.022999999999996</v>
       </c>
       <c r="C20">
-        <v>3.1419999999999999</v>
+        <v>3.133</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +716,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>74.230999999999995</v>
+        <v>75.218000000000004</v>
       </c>
       <c r="C21">
-        <v>3.2160000000000002</v>
+        <v>3.2069999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +727,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>73.513000000000005</v>
+        <v>74.489999999999995</v>
       </c>
       <c r="C22">
-        <v>3.2</v>
+        <v>3.1909999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +738,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>72.917000000000002</v>
+        <v>73.882999999999996</v>
       </c>
       <c r="C23">
-        <v>3.286</v>
+        <v>3.2770000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +749,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>72.403999999999996</v>
+        <v>73.361000000000004</v>
       </c>
       <c r="C24">
-        <v>3.581</v>
+        <v>3.5750000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +760,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>71.869</v>
+        <v>72.819000000000003</v>
       </c>
       <c r="C25">
-        <v>4.2060000000000004</v>
+        <v>4.1959999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +771,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>71.427000000000007</v>
+        <v>72.376999999999995</v>
       </c>
       <c r="C26">
-        <v>4.6379999999999999</v>
+        <v>4.6210000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +782,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>71.064999999999998</v>
+        <v>72.018000000000001</v>
       </c>
       <c r="C27">
-        <v>4.2169999999999996</v>
+        <v>4.2060000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +793,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>70.665000000000006</v>
+        <v>71.625</v>
       </c>
       <c r="C28">
-        <v>3.4769999999999999</v>
+        <v>3.4649999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +804,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>70.352000000000004</v>
+        <v>71.302999999999997</v>
       </c>
       <c r="C29">
-        <v>3.2360000000000002</v>
+        <v>3.2290000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +815,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.05</v>
+        <v>70.977000000000004</v>
       </c>
       <c r="C30">
-        <v>3.2330000000000001</v>
+        <v>3.2290000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +826,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>69.691999999999993</v>
+        <v>70.603999999999999</v>
       </c>
       <c r="C31">
-        <v>3.395</v>
+        <v>3.3940000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +837,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.394999999999996</v>
+        <v>70.287999999999997</v>
       </c>
       <c r="C32">
-        <v>3.6</v>
+        <v>3.6019999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +848,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.111999999999995</v>
+        <v>69.989000000000004</v>
       </c>
       <c r="C33">
-        <v>3.6619999999999999</v>
+        <v>3.6629999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,7 +859,7 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>68.819000000000003</v>
+        <v>69.686000000000007</v>
       </c>
       <c r="C34">
         <v>3.633</v>
@@ -841,10 +870,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.576999999999998</v>
+        <v>69.424000000000007</v>
       </c>
       <c r="C35">
-        <v>3.68</v>
+        <v>3.6819999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +881,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.326999999999998</v>
+        <v>69.14</v>
       </c>
       <c r="C36">
-        <v>3.8519999999999999</v>
+        <v>3.8530000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +892,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.039000000000001</v>
+        <v>68.841999999999999</v>
       </c>
       <c r="C37">
-        <v>4.3949999999999996</v>
+        <v>4.3970000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +903,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>67.760000000000005</v>
+        <v>68.566999999999993</v>
       </c>
       <c r="C38">
-        <v>4.827</v>
+        <v>4.8239999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +914,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.501000000000005</v>
+        <v>68.298000000000002</v>
       </c>
       <c r="C39">
-        <v>4.3579999999999997</v>
+        <v>4.3609999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +925,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.257000000000005</v>
+        <v>68.040000000000006</v>
       </c>
       <c r="C40">
-        <v>3.45</v>
+        <v>3.444</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +936,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.040999999999997</v>
+        <v>67.805999999999997</v>
       </c>
       <c r="C41">
-        <v>3.1749999999999998</v>
+        <v>3.1669999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +947,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.793999999999997</v>
+        <v>67.537999999999997</v>
       </c>
       <c r="C42">
-        <v>3.157</v>
+        <v>3.1480000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +958,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.492000000000004</v>
+        <v>67.228999999999999</v>
       </c>
       <c r="C43">
-        <v>3.286</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +969,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.233000000000004</v>
+        <v>66.98</v>
       </c>
       <c r="C44">
-        <v>3.492</v>
+        <v>3.4830000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +980,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66</v>
+        <v>66.739999999999995</v>
       </c>
       <c r="C45">
-        <v>3.5550000000000002</v>
+        <v>3.544</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +991,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.787000000000006</v>
+        <v>66.524000000000001</v>
       </c>
       <c r="C46">
-        <v>3.5369999999999999</v>
+        <v>3.5249999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +1002,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.588999999999999</v>
+        <v>66.316000000000003</v>
       </c>
       <c r="C47">
-        <v>3.5880000000000001</v>
+        <v>3.5779999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +1013,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.355000000000004</v>
+        <v>66.070999999999998</v>
       </c>
       <c r="C48">
-        <v>3.726</v>
+        <v>3.7130000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +1024,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.102000000000004</v>
+        <v>65.819000000000003</v>
       </c>
       <c r="C49">
-        <v>4.2789999999999999</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1035,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>64.849999999999994</v>
+        <v>65.572999999999993</v>
       </c>
       <c r="C50">
-        <v>4.7450000000000001</v>
+        <v>4.7320000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1046,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.647000000000006</v>
+        <v>65.353999999999999</v>
       </c>
       <c r="C51">
-        <v>4.3410000000000002</v>
+        <v>4.3250000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1057,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.447000000000003</v>
+        <v>65.143000000000001</v>
       </c>
       <c r="C52">
-        <v>3.4910000000000001</v>
+        <v>3.476</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1068,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.257000000000005</v>
+        <v>64.944000000000003</v>
       </c>
       <c r="C53">
-        <v>3.1459999999999999</v>
+        <v>3.1320000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1079,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.016999999999996</v>
+        <v>64.697000000000003</v>
       </c>
       <c r="C54">
-        <v>3.1030000000000002</v>
+        <v>3.0939999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1090,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>63.771000000000001</v>
+        <v>64.450999999999993</v>
       </c>
       <c r="C55">
-        <v>3.2170000000000001</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1101,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>63.555999999999997</v>
+        <v>64.239999999999995</v>
       </c>
       <c r="C56">
-        <v>3.4510000000000001</v>
+        <v>3.4460000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1112,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.350999999999999</v>
+        <v>64.040999999999997</v>
       </c>
       <c r="C57">
-        <v>3.49</v>
+        <v>3.4849999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1405,49 +1434,1237 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4BC497-8C70-4D6A-BE07-92F36FE7AF74}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B2">
+        <v>63.533999999999999</v>
+      </c>
+      <c r="C2">
+        <v>2.9498000000000002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B3">
+        <v>60.07</v>
+      </c>
+      <c r="C3">
+        <v>3.1211000000000002</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B4">
+        <v>59.478999999999999</v>
+      </c>
+      <c r="C4">
+        <v>3.7837999999999998</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B5">
+        <v>57.866</v>
+      </c>
+      <c r="C5">
+        <v>4.1501999999999999</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B6">
+        <v>60.26</v>
+      </c>
+      <c r="C6">
+        <v>7.7126000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B7">
+        <v>64.522999999999996</v>
+      </c>
+      <c r="C7">
+        <v>3.8382000000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B8">
+        <v>90.997</v>
+      </c>
+      <c r="C8">
+        <v>3.0581999999999998</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B9">
+        <v>98.06</v>
+      </c>
+      <c r="C9">
+        <v>2.7736999999999998</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B10">
+        <v>98.513999999999996</v>
+      </c>
+      <c r="C10">
+        <v>2.8881999999999999</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B11">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="C11">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B12">
+        <v>79.22</v>
+      </c>
+      <c r="C12">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B13">
+        <v>82.451999999999998</v>
+      </c>
+      <c r="C13">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B14">
+        <v>97.36</v>
+      </c>
+      <c r="C14">
+        <v>2.8264999999999998</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B15">
+        <v>94.614999999999995</v>
+      </c>
+      <c r="C15">
+        <v>2.9119999999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>46327</v>
+      </c>
+      <c r="B16">
+        <v>91.25</v>
+      </c>
+      <c r="C16">
+        <v>3.0430000000000001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46357</v>
+      </c>
+      <c r="B17">
+        <v>87.974999999999994</v>
+      </c>
+      <c r="C17">
+        <v>3.395</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46388</v>
+      </c>
+      <c r="B18">
+        <v>85.253</v>
+      </c>
+      <c r="C18">
+        <v>3.7410000000000001</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46419</v>
+      </c>
+      <c r="B19">
+        <v>83.382999999999996</v>
+      </c>
+      <c r="C19">
+        <v>3.4390000000000001</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46447</v>
+      </c>
+      <c r="B20">
+        <v>81.358999999999995</v>
+      </c>
+      <c r="C20">
+        <v>2.8119999999999998</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46478</v>
+      </c>
+      <c r="B21">
+        <v>79.605999999999995</v>
+      </c>
+      <c r="C21">
+        <v>2.71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46508</v>
+      </c>
+      <c r="B22">
+        <v>78.314999999999998</v>
+      </c>
+      <c r="C22">
+        <v>2.7450000000000001</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>46539</v>
+      </c>
+      <c r="B23">
+        <v>77.134</v>
+      </c>
+      <c r="C23">
+        <v>2.907</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>46569</v>
+      </c>
+      <c r="B24">
+        <v>76.022999999999996</v>
+      </c>
+      <c r="C24">
+        <v>3.133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>46600</v>
+      </c>
+      <c r="B25">
+        <v>75.218000000000004</v>
+      </c>
+      <c r="C25">
+        <v>3.2069999999999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46631</v>
+      </c>
+      <c r="B26">
+        <v>74.489999999999995</v>
+      </c>
+      <c r="C26">
+        <v>3.1909999999999998</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46661</v>
+      </c>
+      <c r="B27">
+        <v>73.882999999999996</v>
+      </c>
+      <c r="C27">
+        <v>3.2770000000000001</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46692</v>
+      </c>
+      <c r="B28">
+        <v>73.361000000000004</v>
+      </c>
+      <c r="C28">
+        <v>3.5750000000000002</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>46722</v>
+      </c>
+      <c r="B29">
+        <v>72.819000000000003</v>
+      </c>
+      <c r="C29">
+        <v>4.1959999999999997</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>46753</v>
+      </c>
+      <c r="B30">
+        <v>72.376999999999995</v>
+      </c>
+      <c r="C30">
+        <v>4.6210000000000004</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46784</v>
+      </c>
+      <c r="B31">
+        <v>72.018000000000001</v>
+      </c>
+      <c r="C31">
+        <v>4.2060000000000004</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>46813</v>
+      </c>
+      <c r="B32">
+        <v>71.625</v>
+      </c>
+      <c r="C32">
+        <v>3.4649999999999999</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>46844</v>
+      </c>
+      <c r="B33">
+        <v>71.302999999999997</v>
+      </c>
+      <c r="C33">
+        <v>3.2290000000000001</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>46874</v>
+      </c>
+      <c r="B34">
+        <v>70.977000000000004</v>
+      </c>
+      <c r="C34">
+        <v>3.2290000000000001</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>46905</v>
+      </c>
+      <c r="B35">
+        <v>70.603999999999999</v>
+      </c>
+      <c r="C35">
+        <v>3.3940000000000001</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46935</v>
+      </c>
+      <c r="B36">
+        <v>70.287999999999997</v>
+      </c>
+      <c r="C36">
+        <v>3.6019999999999999</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>46966</v>
+      </c>
+      <c r="B37">
+        <v>69.989000000000004</v>
+      </c>
+      <c r="C37">
+        <v>3.6629999999999998</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>46997</v>
+      </c>
+      <c r="B38">
+        <v>69.686000000000007</v>
+      </c>
+      <c r="C38">
+        <v>3.633</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>47027</v>
+      </c>
+      <c r="B39">
+        <v>69.424000000000007</v>
+      </c>
+      <c r="C39">
+        <v>3.6819999999999999</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>47058</v>
+      </c>
+      <c r="B40">
+        <v>69.14</v>
+      </c>
+      <c r="C40">
+        <v>3.8530000000000002</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>47088</v>
+      </c>
+      <c r="B41">
+        <v>68.841999999999999</v>
+      </c>
+      <c r="C41">
+        <v>4.3970000000000002</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>47119</v>
+      </c>
+      <c r="B42">
+        <v>68.566999999999993</v>
+      </c>
+      <c r="C42">
+        <v>4.8239999999999998</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>47150</v>
+      </c>
+      <c r="B43">
+        <v>68.298000000000002</v>
+      </c>
+      <c r="C43">
+        <v>4.3609999999999998</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>47178</v>
+      </c>
+      <c r="B44">
+        <v>68.040000000000006</v>
+      </c>
+      <c r="C44">
+        <v>3.444</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>47209</v>
+      </c>
+      <c r="B45">
+        <v>67.805999999999997</v>
+      </c>
+      <c r="C45">
+        <v>3.1669999999999998</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>47239</v>
+      </c>
+      <c r="B46">
+        <v>67.537999999999997</v>
+      </c>
+      <c r="C46">
+        <v>3.1480000000000001</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>47270</v>
+      </c>
+      <c r="B47">
+        <v>67.228999999999999</v>
+      </c>
+      <c r="C47">
+        <v>3.278</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47300</v>
+      </c>
+      <c r="B48">
+        <v>66.98</v>
+      </c>
+      <c r="C48">
+        <v>3.4830000000000001</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47331</v>
+      </c>
+      <c r="B49">
+        <v>66.739999999999995</v>
+      </c>
+      <c r="C49">
+        <v>3.544</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>47362</v>
+      </c>
+      <c r="B50">
+        <v>66.524000000000001</v>
+      </c>
+      <c r="C50">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47392</v>
+      </c>
+      <c r="B51">
+        <v>66.316000000000003</v>
+      </c>
+      <c r="C51">
+        <v>3.5779999999999998</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>47423</v>
+      </c>
+      <c r="B52">
+        <v>66.070999999999998</v>
+      </c>
+      <c r="C52">
+        <v>3.7130000000000001</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>47453</v>
+      </c>
+      <c r="B53">
+        <v>65.819000000000003</v>
+      </c>
+      <c r="C53">
+        <v>4.266</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>47484</v>
+      </c>
+      <c r="B54">
+        <v>65.572999999999993</v>
+      </c>
+      <c r="C54">
+        <v>4.7320000000000002</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>47515</v>
+      </c>
+      <c r="B55">
+        <v>65.353999999999999</v>
+      </c>
+      <c r="C55">
+        <v>4.3250000000000002</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>47543</v>
+      </c>
+      <c r="B56">
+        <v>65.143000000000001</v>
+      </c>
+      <c r="C56">
+        <v>3.476</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>47574</v>
+      </c>
+      <c r="B57">
+        <v>64.944000000000003</v>
+      </c>
+      <c r="C57">
+        <v>3.1320000000000001</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>47604</v>
+      </c>
+      <c r="B58">
+        <v>64.697000000000003</v>
+      </c>
+      <c r="C58">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>47635</v>
+      </c>
+      <c r="B59">
+        <v>64.450999999999993</v>
+      </c>
+      <c r="C59">
+        <v>3.21</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>47665</v>
+      </c>
+      <c r="B60">
+        <v>64.239999999999995</v>
+      </c>
+      <c r="C60">
+        <v>3.4460000000000002</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>47696</v>
+      </c>
+      <c r="B61">
+        <v>64.040999999999997</v>
+      </c>
+      <c r="C61">
+        <v>3.4849999999999999</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1742,10 +2959,63 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1762,20 +3032,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBCDA1A9-594A-4E3C-ACDC-F9AB9F0C4CCE}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C84EA50-D412-49E0-953F-B8FCFC57D1E0}"/>
   <bookViews>
-    <workbookView xWindow="-19400" yWindow="14380" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>oil_price</t>
   </si>
@@ -43,33 +42,6 @@
   </si>
   <si>
     <t>gas_price</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>WTI</t>
-  </si>
-  <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>SourceWTI</t>
-  </si>
-  <si>
-    <t>SourceHH</t>
-  </si>
-  <si>
-    <t>MaxAsOfDate</t>
-  </si>
-  <si>
-    <t>SETTLED</t>
-  </si>
-  <si>
-    <t>STRIP</t>
-  </si>
-  <si>
-    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -107,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -122,7 +94,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>97.36</v>
+        <v>95.87</v>
       </c>
       <c r="C10">
-        <v>2.8264999999999998</v>
+        <v>2.7885</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -606,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>94.614999999999995</v>
+        <v>91.203000000000003</v>
       </c>
       <c r="C11">
-        <v>2.9119999999999999</v>
+        <v>2.8359999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -617,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>91.25</v>
+        <v>88.488</v>
       </c>
       <c r="C12">
-        <v>3.0430000000000001</v>
+        <v>2.9929999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -628,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>87.974999999999994</v>
+        <v>85.741</v>
       </c>
       <c r="C13">
-        <v>3.395</v>
+        <v>3.3660000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -639,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>85.253</v>
+        <v>83.495000000000005</v>
       </c>
       <c r="C14">
-        <v>3.7410000000000001</v>
+        <v>3.7389999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -650,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>83.382999999999996</v>
+        <v>81.989000000000004</v>
       </c>
       <c r="C15">
-        <v>3.4390000000000001</v>
+        <v>3.4180000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -661,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>81.358999999999995</v>
+        <v>80.387</v>
       </c>
       <c r="C16">
-        <v>2.8119999999999998</v>
+        <v>2.782</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -672,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>79.605999999999995</v>
+        <v>79.004999999999995</v>
       </c>
       <c r="C17">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -683,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>78.314999999999998</v>
+        <v>77.974000000000004</v>
       </c>
       <c r="C18">
-        <v>2.7450000000000001</v>
+        <v>2.7149999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -694,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>77.134</v>
+        <v>76.997</v>
       </c>
       <c r="C19">
-        <v>2.907</v>
+        <v>2.8780000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -705,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>76.022999999999996</v>
+        <v>76.031000000000006</v>
       </c>
       <c r="C20">
-        <v>3.133</v>
+        <v>3.1080000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -716,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>75.218000000000004</v>
+        <v>75.307000000000002</v>
       </c>
       <c r="C21">
-        <v>3.2069999999999999</v>
+        <v>3.1850000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -727,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>74.489999999999995</v>
+        <v>74.63</v>
       </c>
       <c r="C22">
-        <v>3.1909999999999998</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -738,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>73.882999999999996</v>
+        <v>74.043000000000006</v>
       </c>
       <c r="C23">
-        <v>3.2770000000000001</v>
+        <v>3.2559999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -749,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>73.361000000000004</v>
+        <v>73.521000000000001</v>
       </c>
       <c r="C24">
-        <v>3.5750000000000002</v>
+        <v>3.552</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -760,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>72.819000000000003</v>
+        <v>72.983000000000004</v>
       </c>
       <c r="C25">
-        <v>4.1959999999999997</v>
+        <v>4.1740000000000004</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -771,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>72.376999999999995</v>
+        <v>72.546999999999997</v>
       </c>
       <c r="C26">
-        <v>4.6210000000000004</v>
+        <v>4.6050000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -782,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>72.018000000000001</v>
+        <v>72.185000000000002</v>
       </c>
       <c r="C27">
-        <v>4.2060000000000004</v>
+        <v>4.194</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -793,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>71.625</v>
+        <v>71.775000000000006</v>
       </c>
       <c r="C28">
-        <v>3.4649999999999999</v>
+        <v>3.4540000000000002</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -804,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>71.302999999999997</v>
+        <v>71.436000000000007</v>
       </c>
       <c r="C29">
-        <v>3.2290000000000001</v>
+        <v>3.2189999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -815,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.977000000000004</v>
+        <v>71.114999999999995</v>
       </c>
       <c r="C30">
-        <v>3.2290000000000001</v>
+        <v>3.2229999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -826,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.603999999999999</v>
+        <v>70.733999999999995</v>
       </c>
       <c r="C31">
-        <v>3.3940000000000001</v>
+        <v>3.3879999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -837,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>70.287999999999997</v>
+        <v>70.421999999999997</v>
       </c>
       <c r="C32">
-        <v>3.6019999999999999</v>
+        <v>3.5960000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -848,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.989000000000004</v>
+        <v>70.129000000000005</v>
       </c>
       <c r="C33">
-        <v>3.6629999999999998</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -859,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.686000000000007</v>
+        <v>69.825999999999993</v>
       </c>
       <c r="C34">
-        <v>3.633</v>
+        <v>3.6280000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -870,7 +841,7 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.424000000000007</v>
+        <v>69.563999999999993</v>
       </c>
       <c r="C35">
         <v>3.6819999999999999</v>
@@ -881,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.14</v>
+        <v>69.28</v>
       </c>
       <c r="C36">
-        <v>3.8530000000000002</v>
+        <v>3.8559999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -892,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.841999999999999</v>
+        <v>68.978999999999999</v>
       </c>
       <c r="C37">
-        <v>4.3970000000000002</v>
+        <v>4.3959999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -903,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.566999999999993</v>
+        <v>68.697000000000003</v>
       </c>
       <c r="C38">
-        <v>4.8239999999999998</v>
+        <v>4.8259999999999996</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -914,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.298000000000002</v>
+        <v>68.424999999999997</v>
       </c>
       <c r="C39">
-        <v>4.3609999999999998</v>
+        <v>4.3650000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -925,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.040000000000006</v>
+        <v>68.16</v>
       </c>
       <c r="C40">
-        <v>3.444</v>
+        <v>3.4449999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -936,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.805999999999997</v>
+        <v>67.929000000000002</v>
       </c>
       <c r="C41">
-        <v>3.1669999999999998</v>
+        <v>3.1680000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.537999999999997</v>
+        <v>67.676000000000002</v>
       </c>
       <c r="C42">
-        <v>3.1480000000000001</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -958,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.228999999999999</v>
+        <v>67.388999999999996</v>
       </c>
       <c r="C43">
-        <v>3.278</v>
+        <v>3.2789999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -969,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.98</v>
+        <v>67.137</v>
       </c>
       <c r="C44">
-        <v>3.4830000000000001</v>
+        <v>3.484</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -980,7 +951,7 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.739999999999995</v>
+        <v>66.89</v>
       </c>
       <c r="C45">
         <v>3.544</v>
@@ -991,7 +962,7 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.524000000000001</v>
+        <v>66.674000000000007</v>
       </c>
       <c r="C46">
         <v>3.5249999999999999</v>
@@ -1002,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.316000000000003</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="C47">
-        <v>3.5779999999999998</v>
+        <v>3.581</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1013,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.070999999999998</v>
+        <v>66.200999999999993</v>
       </c>
       <c r="C48">
-        <v>3.7130000000000001</v>
+        <v>3.7170000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1024,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.819000000000003</v>
+        <v>65.948999999999998</v>
       </c>
       <c r="C49">
-        <v>4.266</v>
+        <v>4.2720000000000002</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1035,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.572999999999993</v>
+        <v>65.703000000000003</v>
       </c>
       <c r="C50">
-        <v>4.7320000000000002</v>
+        <v>4.7370000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1046,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.353999999999999</v>
+        <v>65.480999999999995</v>
       </c>
       <c r="C51">
-        <v>4.3250000000000002</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1057,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.143000000000001</v>
+        <v>65.263000000000005</v>
       </c>
       <c r="C52">
-        <v>3.476</v>
+        <v>3.4780000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.944000000000003</v>
+        <v>65.063999999999993</v>
       </c>
       <c r="C53">
-        <v>3.1320000000000001</v>
+        <v>3.1339999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1079,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.697000000000003</v>
+        <v>64.816999999999993</v>
       </c>
       <c r="C54">
-        <v>3.0939999999999999</v>
+        <v>3.097</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1090,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.450999999999993</v>
+        <v>64.570999999999998</v>
       </c>
       <c r="C55">
-        <v>3.21</v>
+        <v>3.2130000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1101,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.239999999999995</v>
+        <v>64.36</v>
       </c>
       <c r="C56">
-        <v>3.4460000000000002</v>
+        <v>3.448</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1112,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.040999999999997</v>
+        <v>64.161000000000001</v>
       </c>
       <c r="C57">
-        <v>3.4849999999999999</v>
+        <v>3.4870000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1431,1236 +1402,6 @@
   <ignoredErrors>
     <ignoredError sqref="A57:A85 A2:A55 A56" numberStoredAsText="1"/>
   </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4BC497-8C70-4D6A-BE07-92F36FE7AF74}">
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B2">
-        <v>63.533999999999999</v>
-      </c>
-      <c r="C2">
-        <v>2.9498000000000002</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B3">
-        <v>60.07</v>
-      </c>
-      <c r="C3">
-        <v>3.1211000000000002</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>45962</v>
-      </c>
-      <c r="B4">
-        <v>59.478999999999999</v>
-      </c>
-      <c r="C4">
-        <v>3.7837999999999998</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>45992</v>
-      </c>
-      <c r="B5">
-        <v>57.866</v>
-      </c>
-      <c r="C5">
-        <v>4.1501999999999999</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B6">
-        <v>60.26</v>
-      </c>
-      <c r="C6">
-        <v>7.7126000000000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B7">
-        <v>64.522999999999996</v>
-      </c>
-      <c r="C7">
-        <v>3.8382000000000001</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46082</v>
-      </c>
-      <c r="B8">
-        <v>90.997</v>
-      </c>
-      <c r="C8">
-        <v>3.0581999999999998</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B9">
-        <v>98.06</v>
-      </c>
-      <c r="C9">
-        <v>2.7736999999999998</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B10">
-        <v>98.513999999999996</v>
-      </c>
-      <c r="C10">
-        <v>2.8881999999999999</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B11">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="C11">
-        <v>3.1429999999999998</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>46204</v>
-      </c>
-      <c r="B12">
-        <v>79.22</v>
-      </c>
-      <c r="C12">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B13">
-        <v>82.451999999999998</v>
-      </c>
-      <c r="C13">
-        <v>2.7410000000000001</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>46266</v>
-      </c>
-      <c r="B14">
-        <v>97.36</v>
-      </c>
-      <c r="C14">
-        <v>2.8264999999999998</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46296</v>
-      </c>
-      <c r="B15">
-        <v>94.614999999999995</v>
-      </c>
-      <c r="C15">
-        <v>2.9119999999999999</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>46327</v>
-      </c>
-      <c r="B16">
-        <v>91.25</v>
-      </c>
-      <c r="C16">
-        <v>3.0430000000000001</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>46357</v>
-      </c>
-      <c r="B17">
-        <v>87.974999999999994</v>
-      </c>
-      <c r="C17">
-        <v>3.395</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>46388</v>
-      </c>
-      <c r="B18">
-        <v>85.253</v>
-      </c>
-      <c r="C18">
-        <v>3.7410000000000001</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>46419</v>
-      </c>
-      <c r="B19">
-        <v>83.382999999999996</v>
-      </c>
-      <c r="C19">
-        <v>3.4390000000000001</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46447</v>
-      </c>
-      <c r="B20">
-        <v>81.358999999999995</v>
-      </c>
-      <c r="C20">
-        <v>2.8119999999999998</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>46478</v>
-      </c>
-      <c r="B21">
-        <v>79.605999999999995</v>
-      </c>
-      <c r="C21">
-        <v>2.71</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>46508</v>
-      </c>
-      <c r="B22">
-        <v>78.314999999999998</v>
-      </c>
-      <c r="C22">
-        <v>2.7450000000000001</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>46539</v>
-      </c>
-      <c r="B23">
-        <v>77.134</v>
-      </c>
-      <c r="C23">
-        <v>2.907</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46569</v>
-      </c>
-      <c r="B24">
-        <v>76.022999999999996</v>
-      </c>
-      <c r="C24">
-        <v>3.133</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>46600</v>
-      </c>
-      <c r="B25">
-        <v>75.218000000000004</v>
-      </c>
-      <c r="C25">
-        <v>3.2069999999999999</v>
-      </c>
-      <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>46631</v>
-      </c>
-      <c r="B26">
-        <v>74.489999999999995</v>
-      </c>
-      <c r="C26">
-        <v>3.1909999999999998</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>46661</v>
-      </c>
-      <c r="B27">
-        <v>73.882999999999996</v>
-      </c>
-      <c r="C27">
-        <v>3.2770000000000001</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>46692</v>
-      </c>
-      <c r="B28">
-        <v>73.361000000000004</v>
-      </c>
-      <c r="C28">
-        <v>3.5750000000000002</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>46722</v>
-      </c>
-      <c r="B29">
-        <v>72.819000000000003</v>
-      </c>
-      <c r="C29">
-        <v>4.1959999999999997</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>46753</v>
-      </c>
-      <c r="B30">
-        <v>72.376999999999995</v>
-      </c>
-      <c r="C30">
-        <v>4.6210000000000004</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>46784</v>
-      </c>
-      <c r="B31">
-        <v>72.018000000000001</v>
-      </c>
-      <c r="C31">
-        <v>4.2060000000000004</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>46813</v>
-      </c>
-      <c r="B32">
-        <v>71.625</v>
-      </c>
-      <c r="C32">
-        <v>3.4649999999999999</v>
-      </c>
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>46844</v>
-      </c>
-      <c r="B33">
-        <v>71.302999999999997</v>
-      </c>
-      <c r="C33">
-        <v>3.2290000000000001</v>
-      </c>
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>46874</v>
-      </c>
-      <c r="B34">
-        <v>70.977000000000004</v>
-      </c>
-      <c r="C34">
-        <v>3.2290000000000001</v>
-      </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>46905</v>
-      </c>
-      <c r="B35">
-        <v>70.603999999999999</v>
-      </c>
-      <c r="C35">
-        <v>3.3940000000000001</v>
-      </c>
-      <c r="D35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>46935</v>
-      </c>
-      <c r="B36">
-        <v>70.287999999999997</v>
-      </c>
-      <c r="C36">
-        <v>3.6019999999999999</v>
-      </c>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>46966</v>
-      </c>
-      <c r="B37">
-        <v>69.989000000000004</v>
-      </c>
-      <c r="C37">
-        <v>3.6629999999999998</v>
-      </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>46997</v>
-      </c>
-      <c r="B38">
-        <v>69.686000000000007</v>
-      </c>
-      <c r="C38">
-        <v>3.633</v>
-      </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>47027</v>
-      </c>
-      <c r="B39">
-        <v>69.424000000000007</v>
-      </c>
-      <c r="C39">
-        <v>3.6819999999999999</v>
-      </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>47058</v>
-      </c>
-      <c r="B40">
-        <v>69.14</v>
-      </c>
-      <c r="C40">
-        <v>3.8530000000000002</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>47088</v>
-      </c>
-      <c r="B41">
-        <v>68.841999999999999</v>
-      </c>
-      <c r="C41">
-        <v>4.3970000000000002</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>47119</v>
-      </c>
-      <c r="B42">
-        <v>68.566999999999993</v>
-      </c>
-      <c r="C42">
-        <v>4.8239999999999998</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>47150</v>
-      </c>
-      <c r="B43">
-        <v>68.298000000000002</v>
-      </c>
-      <c r="C43">
-        <v>4.3609999999999998</v>
-      </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>47178</v>
-      </c>
-      <c r="B44">
-        <v>68.040000000000006</v>
-      </c>
-      <c r="C44">
-        <v>3.444</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>47209</v>
-      </c>
-      <c r="B45">
-        <v>67.805999999999997</v>
-      </c>
-      <c r="C45">
-        <v>3.1669999999999998</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>47239</v>
-      </c>
-      <c r="B46">
-        <v>67.537999999999997</v>
-      </c>
-      <c r="C46">
-        <v>3.1480000000000001</v>
-      </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>47270</v>
-      </c>
-      <c r="B47">
-        <v>67.228999999999999</v>
-      </c>
-      <c r="C47">
-        <v>3.278</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>47300</v>
-      </c>
-      <c r="B48">
-        <v>66.98</v>
-      </c>
-      <c r="C48">
-        <v>3.4830000000000001</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>47331</v>
-      </c>
-      <c r="B49">
-        <v>66.739999999999995</v>
-      </c>
-      <c r="C49">
-        <v>3.544</v>
-      </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>47362</v>
-      </c>
-      <c r="B50">
-        <v>66.524000000000001</v>
-      </c>
-      <c r="C50">
-        <v>3.5249999999999999</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>47392</v>
-      </c>
-      <c r="B51">
-        <v>66.316000000000003</v>
-      </c>
-      <c r="C51">
-        <v>3.5779999999999998</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>47423</v>
-      </c>
-      <c r="B52">
-        <v>66.070999999999998</v>
-      </c>
-      <c r="C52">
-        <v>3.7130000000000001</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>47453</v>
-      </c>
-      <c r="B53">
-        <v>65.819000000000003</v>
-      </c>
-      <c r="C53">
-        <v>4.266</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>47484</v>
-      </c>
-      <c r="B54">
-        <v>65.572999999999993</v>
-      </c>
-      <c r="C54">
-        <v>4.7320000000000002</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>47515</v>
-      </c>
-      <c r="B55">
-        <v>65.353999999999999</v>
-      </c>
-      <c r="C55">
-        <v>4.3250000000000002</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>47543</v>
-      </c>
-      <c r="B56">
-        <v>65.143000000000001</v>
-      </c>
-      <c r="C56">
-        <v>3.476</v>
-      </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>47574</v>
-      </c>
-      <c r="B57">
-        <v>64.944000000000003</v>
-      </c>
-      <c r="C57">
-        <v>3.1320000000000001</v>
-      </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>47604</v>
-      </c>
-      <c r="B58">
-        <v>64.697000000000003</v>
-      </c>
-      <c r="C58">
-        <v>3.0939999999999999</v>
-      </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>47635</v>
-      </c>
-      <c r="B59">
-        <v>64.450999999999993</v>
-      </c>
-      <c r="C59">
-        <v>3.21</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>47665</v>
-      </c>
-      <c r="B60">
-        <v>64.239999999999995</v>
-      </c>
-      <c r="C60">
-        <v>3.4460000000000002</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>47696</v>
-      </c>
-      <c r="B61">
-        <v>64.040999999999997</v>
-      </c>
-      <c r="C61">
-        <v>3.4849999999999999</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="6">
-        <v>46283</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2960,6 +1701,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
@@ -2992,15 +1742,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
@@ -3021,6 +1762,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3029,12 +1778,4 @@
     <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C84EA50-D412-49E0-953F-B8FCFC57D1E0}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C802D0-CB91-4BC2-9730-074A52FF4697}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>95.87</v>
+        <v>95.753</v>
       </c>
       <c r="C10">
-        <v>2.7885</v>
+        <v>2.8820000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>91.203000000000003</v>
+        <v>91.195999999999998</v>
       </c>
       <c r="C11">
-        <v>2.8359999999999999</v>
+        <v>3.0230000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>88.488</v>
+        <v>88.905000000000001</v>
       </c>
       <c r="C12">
-        <v>2.9929999999999999</v>
+        <v>3.153</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>85.741</v>
+        <v>86.412000000000006</v>
       </c>
       <c r="C13">
-        <v>3.3660000000000001</v>
+        <v>3.4929999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>83.495000000000005</v>
+        <v>84.278000000000006</v>
       </c>
       <c r="C14">
-        <v>3.7389999999999999</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>81.989000000000004</v>
+        <v>82.766999999999996</v>
       </c>
       <c r="C15">
-        <v>3.4180000000000001</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>80.387</v>
+        <v>81.087000000000003</v>
       </c>
       <c r="C16">
-        <v>2.782</v>
+        <v>2.851</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>79.004999999999995</v>
+        <v>79.578000000000003</v>
       </c>
       <c r="C17">
-        <v>2.68</v>
+        <v>2.7309999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>77.974000000000004</v>
+        <v>78.424999999999997</v>
       </c>
       <c r="C18">
-        <v>2.7149999999999999</v>
+        <v>2.7559999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>76.997</v>
+        <v>77.319999999999993</v>
       </c>
       <c r="C19">
-        <v>2.8780000000000001</v>
+        <v>2.9129999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>76.031000000000006</v>
+        <v>76.22</v>
       </c>
       <c r="C20">
-        <v>3.1080000000000001</v>
+        <v>3.1379999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>75.307000000000002</v>
+        <v>75.385999999999996</v>
       </c>
       <c r="C21">
-        <v>3.1850000000000001</v>
+        <v>3.2120000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>74.63</v>
+        <v>74.582999999999998</v>
       </c>
       <c r="C22">
-        <v>3.17</v>
+        <v>3.1970000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>74.043000000000006</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="C23">
-        <v>3.2559999999999998</v>
+        <v>3.2839999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>73.521000000000001</v>
+        <v>73.313999999999993</v>
       </c>
       <c r="C24">
-        <v>3.552</v>
+        <v>3.5680000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>72.983000000000004</v>
+        <v>72.710999999999999</v>
       </c>
       <c r="C25">
-        <v>4.1740000000000004</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>72.546999999999997</v>
+        <v>72.222999999999999</v>
       </c>
       <c r="C26">
-        <v>4.6050000000000004</v>
+        <v>4.609</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>72.185000000000002</v>
+        <v>71.828000000000003</v>
       </c>
       <c r="C27">
-        <v>4.194</v>
+        <v>4.2069999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>71.775000000000006</v>
+        <v>71.388000000000005</v>
       </c>
       <c r="C28">
-        <v>3.4540000000000002</v>
+        <v>3.4769999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>71.436000000000007</v>
+        <v>71.025999999999996</v>
       </c>
       <c r="C29">
-        <v>3.2189999999999999</v>
+        <v>3.246</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>71.114999999999995</v>
+        <v>70.679000000000002</v>
       </c>
       <c r="C30">
-        <v>3.2229999999999999</v>
+        <v>3.2429999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.733999999999995</v>
+        <v>70.269000000000005</v>
       </c>
       <c r="C31">
-        <v>3.3879999999999999</v>
+        <v>3.403</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>70.421999999999997</v>
+        <v>69.921000000000006</v>
       </c>
       <c r="C32">
-        <v>3.5960000000000001</v>
+        <v>3.6120000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>70.129000000000005</v>
+        <v>69.602999999999994</v>
       </c>
       <c r="C33">
-        <v>3.657</v>
+        <v>3.6720000000000002</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.825999999999993</v>
+        <v>69.275000000000006</v>
       </c>
       <c r="C34">
-        <v>3.6280000000000001</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.563999999999993</v>
+        <v>68.988</v>
       </c>
       <c r="C35">
-        <v>3.6819999999999999</v>
+        <v>3.6960000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.28</v>
+        <v>68.683000000000007</v>
       </c>
       <c r="C36">
-        <v>3.8559999999999999</v>
+        <v>3.871</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.978999999999999</v>
+        <v>68.361999999999995</v>
       </c>
       <c r="C37">
-        <v>4.3959999999999999</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.697000000000003</v>
+        <v>68.063000000000002</v>
       </c>
       <c r="C38">
-        <v>4.8259999999999996</v>
+        <v>4.8410000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.424999999999997</v>
+        <v>67.781999999999996</v>
       </c>
       <c r="C39">
-        <v>4.3650000000000002</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.16</v>
+        <v>67.507000000000005</v>
       </c>
       <c r="C40">
-        <v>3.4449999999999998</v>
+        <v>3.4569999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.929000000000002</v>
+        <v>67.260000000000005</v>
       </c>
       <c r="C41">
-        <v>3.1680000000000001</v>
+        <v>3.1779999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.676000000000002</v>
+        <v>66.977999999999994</v>
       </c>
       <c r="C42">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.388999999999996</v>
+        <v>66.673000000000002</v>
       </c>
       <c r="C43">
-        <v>3.2789999999999999</v>
+        <v>3.2869999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.137</v>
+        <v>66.427000000000007</v>
       </c>
       <c r="C44">
-        <v>3.484</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.89</v>
+        <v>66.177000000000007</v>
       </c>
       <c r="C45">
-        <v>3.544</v>
+        <v>3.5529999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.674000000000007</v>
+        <v>65.947000000000003</v>
       </c>
       <c r="C46">
-        <v>3.5249999999999999</v>
+        <v>3.5329999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.459999999999994</v>
+        <v>65.710999999999999</v>
       </c>
       <c r="C47">
-        <v>3.581</v>
+        <v>3.589</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.200999999999993</v>
+        <v>65.42</v>
       </c>
       <c r="C48">
-        <v>3.7170000000000001</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.948999999999998</v>
+        <v>65.156000000000006</v>
       </c>
       <c r="C49">
-        <v>4.2720000000000002</v>
+        <v>4.2809999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.703000000000003</v>
+        <v>64.92</v>
       </c>
       <c r="C50">
-        <v>4.7370000000000001</v>
+        <v>4.7439999999999998</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.480999999999995</v>
+        <v>64.691000000000003</v>
       </c>
       <c r="C51">
-        <v>4.33</v>
+        <v>4.3360000000000003</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.263000000000005</v>
+        <v>64.47</v>
       </c>
       <c r="C52">
-        <v>3.4780000000000002</v>
+        <v>3.4849999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.063999999999993</v>
+        <v>64.263999999999996</v>
       </c>
       <c r="C53">
-        <v>3.1339999999999999</v>
+        <v>3.1429999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.816999999999993</v>
+        <v>64.016999999999996</v>
       </c>
       <c r="C54">
-        <v>3.097</v>
+        <v>3.1059999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.570999999999998</v>
+        <v>63.767000000000003</v>
       </c>
       <c r="C55">
-        <v>3.2130000000000001</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.36</v>
+        <v>63.55</v>
       </c>
       <c r="C56">
-        <v>3.448</v>
+        <v>3.4590000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.161000000000001</v>
+        <v>63.350999999999999</v>
       </c>
       <c r="C57">
-        <v>3.4870000000000001</v>
+        <v>3.4980000000000002</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,6 +1406,48 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1700,49 +1742,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1759,23 +1778,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94C802D0-CB91-4BC2-9730-074A52FF4697}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08949AA3-F29B-45AB-B9AD-6BEAAE818B9C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>95.753</v>
+        <v>95.917000000000002</v>
       </c>
       <c r="C10">
-        <v>2.8820000000000001</v>
+        <v>2.9685000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>91.195999999999998</v>
+        <v>91.064999999999998</v>
       </c>
       <c r="C11">
-        <v>3.0230000000000001</v>
+        <v>3.1960000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>88.905000000000001</v>
+        <v>88.034999999999997</v>
       </c>
       <c r="C12">
-        <v>3.153</v>
+        <v>3.2250000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>86.412000000000006</v>
+        <v>85.361000000000004</v>
       </c>
       <c r="C13">
-        <v>3.4929999999999999</v>
+        <v>3.5339999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>84.278000000000006</v>
+        <v>83.414000000000001</v>
       </c>
       <c r="C14">
-        <v>3.86</v>
+        <v>3.8860000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>82.766999999999996</v>
+        <v>82.177999999999997</v>
       </c>
       <c r="C15">
-        <v>3.528</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>81.087000000000003</v>
+        <v>80.798000000000002</v>
       </c>
       <c r="C16">
-        <v>2.851</v>
+        <v>2.8340000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>79.578000000000003</v>
+        <v>79.546999999999997</v>
       </c>
       <c r="C17">
-        <v>2.7309999999999999</v>
+        <v>2.7120000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>78.424999999999997</v>
+        <v>78.56</v>
       </c>
       <c r="C18">
-        <v>2.7559999999999998</v>
+        <v>2.738</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>77.319999999999993</v>
+        <v>77.596999999999994</v>
       </c>
       <c r="C19">
-        <v>2.9129999999999998</v>
+        <v>2.8980000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>76.22</v>
+        <v>76.611999999999995</v>
       </c>
       <c r="C20">
-        <v>3.1379999999999999</v>
+        <v>3.1309999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>75.385999999999996</v>
+        <v>75.834999999999994</v>
       </c>
       <c r="C21">
-        <v>3.2120000000000002</v>
+        <v>3.2050000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>74.582999999999998</v>
+        <v>75.082999999999998</v>
       </c>
       <c r="C22">
-        <v>3.1970000000000001</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>73.900000000000006</v>
+        <v>74.42</v>
       </c>
       <c r="C23">
-        <v>3.2839999999999998</v>
+        <v>3.2749999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>73.313999999999993</v>
+        <v>73.84</v>
       </c>
       <c r="C24">
-        <v>3.5680000000000001</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>72.710999999999999</v>
+        <v>73.254999999999995</v>
       </c>
       <c r="C25">
-        <v>4.18</v>
+        <v>4.1849999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>72.222999999999999</v>
+        <v>72.772999999999996</v>
       </c>
       <c r="C26">
-        <v>4.609</v>
+        <v>4.6020000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>71.828000000000003</v>
+        <v>72.378</v>
       </c>
       <c r="C27">
-        <v>4.2069999999999999</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>71.388000000000005</v>
+        <v>71.944999999999993</v>
       </c>
       <c r="C28">
-        <v>3.4769999999999999</v>
+        <v>3.476</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>71.025999999999996</v>
+        <v>71.599000000000004</v>
       </c>
       <c r="C29">
-        <v>3.246</v>
+        <v>3.242</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>70.679000000000002</v>
+        <v>71.259</v>
       </c>
       <c r="C30">
-        <v>3.2429999999999999</v>
+        <v>3.2360000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.269000000000005</v>
+        <v>70.844999999999999</v>
       </c>
       <c r="C31">
-        <v>3.403</v>
+        <v>3.391</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>69.921000000000006</v>
+        <v>70.483999999999995</v>
       </c>
       <c r="C32">
-        <v>3.6120000000000001</v>
+        <v>3.5990000000000002</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>69.602999999999994</v>
+        <v>70.143000000000001</v>
       </c>
       <c r="C33">
-        <v>3.6720000000000002</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.275000000000006</v>
+        <v>69.799000000000007</v>
       </c>
       <c r="C34">
-        <v>3.641</v>
+        <v>3.6230000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>68.988</v>
+        <v>69.518000000000001</v>
       </c>
       <c r="C35">
-        <v>3.6960000000000002</v>
+        <v>3.6739999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>68.683000000000007</v>
+        <v>69.209999999999994</v>
       </c>
       <c r="C36">
-        <v>3.871</v>
+        <v>3.847</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.361999999999995</v>
+        <v>68.875</v>
       </c>
       <c r="C37">
-        <v>4.41</v>
+        <v>4.3780000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.063000000000002</v>
+        <v>68.56</v>
       </c>
       <c r="C38">
-        <v>4.8410000000000002</v>
+        <v>4.8209999999999997</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>67.781999999999996</v>
+        <v>68.268000000000001</v>
       </c>
       <c r="C39">
-        <v>4.38</v>
+        <v>4.3609999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.507000000000005</v>
+        <v>67.972999999999999</v>
       </c>
       <c r="C40">
-        <v>3.4569999999999999</v>
+        <v>3.448</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.260000000000005</v>
+        <v>67.694000000000003</v>
       </c>
       <c r="C41">
-        <v>3.1779999999999999</v>
+        <v>3.1739999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>66.977999999999994</v>
+        <v>67.393000000000001</v>
       </c>
       <c r="C42">
-        <v>3.16</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>66.673000000000002</v>
+        <v>67.055000000000007</v>
       </c>
       <c r="C43">
-        <v>3.2869999999999999</v>
+        <v>3.2839999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.427000000000007</v>
+        <v>66.763000000000005</v>
       </c>
       <c r="C44">
-        <v>3.492</v>
+        <v>3.4889999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.177000000000007</v>
+        <v>66.475999999999999</v>
       </c>
       <c r="C45">
-        <v>3.5529999999999999</v>
+        <v>3.5510000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>65.947000000000003</v>
+        <v>66.221000000000004</v>
       </c>
       <c r="C46">
-        <v>3.5329999999999999</v>
+        <v>3.5369999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.710999999999999</v>
+        <v>65.959000000000003</v>
       </c>
       <c r="C47">
-        <v>3.589</v>
+        <v>3.5990000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.42</v>
+        <v>65.62</v>
       </c>
       <c r="C48">
-        <v>3.726</v>
+        <v>3.7360000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.156000000000006</v>
+        <v>65.316000000000003</v>
       </c>
       <c r="C49">
-        <v>4.2809999999999997</v>
+        <v>4.2910000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>64.92</v>
+        <v>65.046999999999997</v>
       </c>
       <c r="C50">
-        <v>4.7439999999999998</v>
+        <v>4.7549999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.691000000000003</v>
+        <v>64.775000000000006</v>
       </c>
       <c r="C51">
-        <v>4.3360000000000003</v>
+        <v>4.343</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.47</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="C52">
-        <v>3.4849999999999999</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.263999999999996</v>
+        <v>64.272999999999996</v>
       </c>
       <c r="C53">
-        <v>3.1429999999999998</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.016999999999996</v>
+        <v>63.984999999999999</v>
       </c>
       <c r="C54">
-        <v>3.1059999999999999</v>
+        <v>3.1139999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>63.767000000000003</v>
+        <v>63.698</v>
       </c>
       <c r="C55">
-        <v>3.222</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>63.55</v>
+        <v>63.444000000000003</v>
       </c>
       <c r="C56">
-        <v>3.4590000000000001</v>
+        <v>3.4670000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.350999999999999</v>
+        <v>63.195999999999998</v>
       </c>
       <c r="C57">
-        <v>3.4980000000000002</v>
+        <v>3.5070000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,15 +1406,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
@@ -1445,6 +1436,15 @@
     </_ApprovalSentBy>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1743,20 +1743,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
     <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08949AA3-F29B-45AB-B9AD-6BEAAE818B9C}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A289A088-7483-43B6-84FF-90952B6A8191}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>95.917000000000002</v>
+        <v>95.944000000000003</v>
       </c>
       <c r="C10">
-        <v>2.9685000000000001</v>
+        <v>2.8704999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>91.064999999999998</v>
+        <v>91.295000000000002</v>
       </c>
       <c r="C11">
-        <v>3.1960000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>88.034999999999997</v>
+        <v>88.393000000000001</v>
       </c>
       <c r="C12">
-        <v>3.2250000000000001</v>
+        <v>3.1059999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>85.361000000000004</v>
+        <v>85.950999999999993</v>
       </c>
       <c r="C13">
-        <v>3.5339999999999998</v>
+        <v>3.452</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>83.414000000000001</v>
+        <v>84.144999999999996</v>
       </c>
       <c r="C14">
-        <v>3.8860000000000001</v>
+        <v>3.8370000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>82.177999999999997</v>
+        <v>82.93</v>
       </c>
       <c r="C15">
-        <v>3.55</v>
+        <v>3.5009999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>80.798000000000002</v>
+        <v>81.558000000000007</v>
       </c>
       <c r="C16">
-        <v>2.8340000000000001</v>
+        <v>2.8039999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>79.546999999999997</v>
+        <v>80.304000000000002</v>
       </c>
       <c r="C17">
-        <v>2.7120000000000002</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>78.56</v>
+        <v>79.31</v>
       </c>
       <c r="C18">
-        <v>2.738</v>
+        <v>2.722</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>77.596999999999994</v>
+        <v>78.340999999999994</v>
       </c>
       <c r="C19">
-        <v>2.8980000000000001</v>
+        <v>2.8849999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>76.611999999999995</v>
+        <v>77.341999999999999</v>
       </c>
       <c r="C20">
-        <v>3.1309999999999998</v>
+        <v>3.1269999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>75.834999999999994</v>
+        <v>76.561999999999998</v>
       </c>
       <c r="C21">
-        <v>3.2050000000000001</v>
+        <v>3.2029999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>75.082999999999998</v>
+        <v>75.8</v>
       </c>
       <c r="C22">
-        <v>3.19</v>
+        <v>3.1880000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>74.42</v>
+        <v>75.12</v>
       </c>
       <c r="C23">
-        <v>3.2749999999999999</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>73.84</v>
+        <v>74.513999999999996</v>
       </c>
       <c r="C24">
-        <v>3.57</v>
+        <v>3.5720000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,7 +731,7 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>73.254999999999995</v>
+        <v>73.903999999999996</v>
       </c>
       <c r="C25">
         <v>4.1849999999999996</v>
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>72.772999999999996</v>
+        <v>73.396000000000001</v>
       </c>
       <c r="C26">
-        <v>4.6020000000000003</v>
+        <v>4.6059999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>72.378</v>
+        <v>72.983000000000004</v>
       </c>
       <c r="C27">
-        <v>4.2</v>
+        <v>4.2009999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>71.944999999999993</v>
+        <v>72.521000000000001</v>
       </c>
       <c r="C28">
-        <v>3.476</v>
+        <v>3.4710000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>71.599000000000004</v>
+        <v>72.14</v>
       </c>
       <c r="C29">
-        <v>3.242</v>
+        <v>3.2450000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>71.259</v>
+        <v>71.771000000000001</v>
       </c>
       <c r="C30">
-        <v>3.2360000000000002</v>
+        <v>3.238</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,7 +797,7 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>70.844999999999999</v>
+        <v>71.334999999999994</v>
       </c>
       <c r="C31">
         <v>3.391</v>
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>70.483999999999995</v>
+        <v>70.974000000000004</v>
       </c>
       <c r="C32">
-        <v>3.5990000000000002</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>70.143000000000001</v>
+        <v>70.63</v>
       </c>
       <c r="C33">
-        <v>3.657</v>
+        <v>3.6579999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>69.799000000000007</v>
+        <v>70.275000000000006</v>
       </c>
       <c r="C34">
-        <v>3.6230000000000002</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.518000000000001</v>
+        <v>69.988</v>
       </c>
       <c r="C35">
-        <v>3.6739999999999999</v>
+        <v>3.6760000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.209999999999994</v>
+        <v>69.680000000000007</v>
       </c>
       <c r="C36">
-        <v>3.847</v>
+        <v>3.8460000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,7 +863,7 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>68.875</v>
+        <v>69.344999999999999</v>
       </c>
       <c r="C37">
         <v>4.3780000000000001</v>
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>68.56</v>
+        <v>69.027000000000001</v>
       </c>
       <c r="C38">
-        <v>4.8209999999999997</v>
+        <v>4.8250000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.268000000000001</v>
+        <v>68.727999999999994</v>
       </c>
       <c r="C39">
-        <v>4.3609999999999998</v>
+        <v>4.3659999999999997</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>67.972999999999999</v>
+        <v>68.44</v>
       </c>
       <c r="C40">
-        <v>3.448</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>67.694000000000003</v>
+        <v>68.177000000000007</v>
       </c>
       <c r="C41">
-        <v>3.1739999999999999</v>
+        <v>3.1779999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.393000000000001</v>
+        <v>67.885000000000005</v>
       </c>
       <c r="C42">
-        <v>3.157</v>
+        <v>3.1619999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.055000000000007</v>
+        <v>67.555000000000007</v>
       </c>
       <c r="C43">
-        <v>3.2839999999999998</v>
+        <v>3.2850000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>66.763000000000005</v>
+        <v>67.266999999999996</v>
       </c>
       <c r="C44">
-        <v>3.4889999999999999</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.475999999999999</v>
+        <v>66.989999999999995</v>
       </c>
       <c r="C45">
-        <v>3.5510000000000002</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.221000000000004</v>
+        <v>66.738</v>
       </c>
       <c r="C46">
-        <v>3.5369999999999999</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>65.959000000000003</v>
+        <v>66.471999999999994</v>
       </c>
       <c r="C47">
-        <v>3.5990000000000002</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>65.62</v>
+        <v>66.14</v>
       </c>
       <c r="C48">
-        <v>3.7360000000000002</v>
+        <v>3.7320000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.316000000000003</v>
+        <v>65.843000000000004</v>
       </c>
       <c r="C49">
-        <v>4.2910000000000004</v>
+        <v>4.2830000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.046999999999997</v>
+        <v>65.59</v>
       </c>
       <c r="C50">
-        <v>4.7549999999999999</v>
+        <v>4.7469999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>64.775000000000006</v>
+        <v>65.325000000000003</v>
       </c>
       <c r="C51">
-        <v>4.343</v>
+        <v>4.3339999999999996</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>64.510000000000005</v>
+        <v>65.063000000000002</v>
       </c>
       <c r="C52">
-        <v>3.492</v>
+        <v>3.4830000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.272999999999996</v>
+        <v>64.835999999999999</v>
       </c>
       <c r="C53">
-        <v>3.1509999999999998</v>
+        <v>3.137</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>63.984999999999999</v>
+        <v>64.555000000000007</v>
       </c>
       <c r="C54">
-        <v>3.1139999999999999</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>63.698</v>
+        <v>64.268000000000001</v>
       </c>
       <c r="C55">
-        <v>3.23</v>
+        <v>3.2160000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>63.444000000000003</v>
+        <v>64.013999999999996</v>
       </c>
       <c r="C56">
-        <v>3.4670000000000001</v>
+        <v>3.4529999999999998</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.195999999999998</v>
+        <v>63.765999999999998</v>
       </c>
       <c r="C57">
-        <v>3.5070000000000001</v>
+        <v>3.4929999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,48 +1406,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1742,26 +1700,49 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1778,4 +1759,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A289A088-7483-43B6-84FF-90952B6A8191}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A535F6A7-8D2F-4EDD-A686-236940F344ED}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="15" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -566,10 +566,10 @@
         <v>46266</v>
       </c>
       <c r="B10">
-        <v>95.944000000000003</v>
+        <v>95.686999999999998</v>
       </c>
       <c r="C10">
-        <v>2.8704999999999998</v>
+        <v>2.9470000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>91.295000000000002</v>
+        <v>89.215000000000003</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>3.0065</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>88.393000000000001</v>
+        <v>87.947999999999993</v>
       </c>
       <c r="C12">
-        <v>3.1059999999999999</v>
+        <v>3.0659999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>85.950999999999993</v>
+        <v>86.846000000000004</v>
       </c>
       <c r="C13">
-        <v>3.452</v>
+        <v>3.3580000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>84.144999999999996</v>
+        <v>85.69</v>
       </c>
       <c r="C14">
-        <v>3.8370000000000002</v>
+        <v>3.7290000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>82.93</v>
+        <v>84.725999999999999</v>
       </c>
       <c r="C15">
-        <v>3.5009999999999999</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>81.558000000000007</v>
+        <v>83.501999999999995</v>
       </c>
       <c r="C16">
-        <v>2.8039999999999998</v>
+        <v>2.7050000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>80.304000000000002</v>
+        <v>82.287000000000006</v>
       </c>
       <c r="C17">
-        <v>2.694</v>
+        <v>2.6179999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>79.31</v>
+        <v>81.293999999999997</v>
       </c>
       <c r="C18">
-        <v>2.722</v>
+        <v>2.649</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>78.340999999999994</v>
+        <v>80.302999999999997</v>
       </c>
       <c r="C19">
-        <v>2.8849999999999998</v>
+        <v>2.8050000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>77.341999999999999</v>
+        <v>79.260000000000005</v>
       </c>
       <c r="C20">
-        <v>3.1269999999999998</v>
+        <v>3.0409999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>76.561999999999998</v>
+        <v>78.412999999999997</v>
       </c>
       <c r="C21">
-        <v>3.2029999999999998</v>
+        <v>3.1150000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>75.8</v>
+        <v>77.557000000000002</v>
       </c>
       <c r="C22">
-        <v>3.1880000000000002</v>
+        <v>3.0960000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>75.12</v>
+        <v>76.783000000000001</v>
       </c>
       <c r="C23">
-        <v>3.274</v>
+        <v>3.1789999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>74.513999999999996</v>
+        <v>76.093000000000004</v>
       </c>
       <c r="C24">
-        <v>3.5720000000000001</v>
+        <v>3.4689999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>73.903999999999996</v>
+        <v>75.364000000000004</v>
       </c>
       <c r="C25">
-        <v>4.1849999999999996</v>
+        <v>4.0620000000000003</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>73.396000000000001</v>
+        <v>74.751000000000005</v>
       </c>
       <c r="C26">
-        <v>4.6059999999999999</v>
+        <v>4.4720000000000004</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +753,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>72.983000000000004</v>
+        <v>74.248000000000005</v>
       </c>
       <c r="C27">
-        <v>4.2009999999999996</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>72.521000000000001</v>
+        <v>73.683000000000007</v>
       </c>
       <c r="C28">
-        <v>3.4710000000000001</v>
+        <v>3.3719999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>72.14</v>
+        <v>73.230999999999995</v>
       </c>
       <c r="C29">
-        <v>3.2450000000000001</v>
+        <v>3.165</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>71.771000000000001</v>
+        <v>72.805000000000007</v>
       </c>
       <c r="C30">
-        <v>3.238</v>
+        <v>3.1629999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>71.334999999999994</v>
+        <v>72.302000000000007</v>
       </c>
       <c r="C31">
-        <v>3.391</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>70.974000000000004</v>
+        <v>71.89</v>
       </c>
       <c r="C32">
-        <v>3.6</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>70.63</v>
+        <v>71.513999999999996</v>
       </c>
       <c r="C33">
-        <v>3.6579999999999999</v>
+        <v>3.5979999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>70.275000000000006</v>
+        <v>71.135000000000005</v>
       </c>
       <c r="C34">
-        <v>3.625</v>
+        <v>3.5680000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>69.988</v>
+        <v>70.814999999999998</v>
       </c>
       <c r="C35">
-        <v>3.6760000000000002</v>
+        <v>3.6190000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>69.680000000000007</v>
+        <v>70.466999999999999</v>
       </c>
       <c r="C36">
-        <v>3.8460000000000001</v>
+        <v>3.7949999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>69.344999999999999</v>
+        <v>70.087000000000003</v>
       </c>
       <c r="C37">
-        <v>4.3780000000000001</v>
+        <v>4.3280000000000003</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>69.027000000000001</v>
+        <v>69.727000000000004</v>
       </c>
       <c r="C38">
-        <v>4.8250000000000002</v>
+        <v>4.7709999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>68.727999999999994</v>
+        <v>69.399000000000001</v>
       </c>
       <c r="C39">
-        <v>4.3659999999999997</v>
+        <v>4.3319999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>68.44</v>
+        <v>69.08</v>
       </c>
       <c r="C40">
-        <v>3.45</v>
+        <v>3.4039999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>68.177000000000007</v>
+        <v>68.786000000000001</v>
       </c>
       <c r="C41">
-        <v>3.1779999999999999</v>
+        <v>3.1440000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>67.885000000000005</v>
+        <v>68.454999999999998</v>
       </c>
       <c r="C42">
-        <v>3.1619999999999999</v>
+        <v>3.1280000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>67.555000000000007</v>
+        <v>68.087999999999994</v>
       </c>
       <c r="C43">
-        <v>3.2850000000000001</v>
+        <v>3.2509999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.266999999999996</v>
+        <v>67.772999999999996</v>
       </c>
       <c r="C44">
-        <v>3.492</v>
+        <v>3.4630000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>66.989999999999995</v>
+        <v>67.456000000000003</v>
       </c>
       <c r="C45">
-        <v>3.55</v>
+        <v>3.5190000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>66.738</v>
+        <v>67.162000000000006</v>
       </c>
       <c r="C46">
-        <v>3.5390000000000001</v>
+        <v>3.5070000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.471999999999994</v>
+        <v>66.855999999999995</v>
       </c>
       <c r="C47">
-        <v>3.6</v>
+        <v>3.5680000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.14</v>
+        <v>66.510000000000005</v>
       </c>
       <c r="C48">
-        <v>3.7320000000000002</v>
+        <v>3.7040000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>65.843000000000004</v>
+        <v>66.201999999999998</v>
       </c>
       <c r="C49">
-        <v>4.2830000000000004</v>
+        <v>4.2510000000000003</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.59</v>
+        <v>65.923000000000002</v>
       </c>
       <c r="C50">
-        <v>4.7469999999999999</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.325000000000003</v>
+        <v>65.638000000000005</v>
       </c>
       <c r="C51">
-        <v>4.3339999999999996</v>
+        <v>4.3120000000000003</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.063000000000002</v>
+        <v>65.352999999999994</v>
       </c>
       <c r="C52">
-        <v>3.4830000000000001</v>
+        <v>3.4660000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>64.835999999999999</v>
+        <v>65.096999999999994</v>
       </c>
       <c r="C53">
-        <v>3.137</v>
+        <v>3.1360000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.555000000000007</v>
+        <v>64.790999999999997</v>
       </c>
       <c r="C54">
-        <v>3.1</v>
+        <v>3.0960000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.268000000000001</v>
+        <v>64.484999999999999</v>
       </c>
       <c r="C55">
-        <v>3.2160000000000002</v>
+        <v>3.2130000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.013999999999996</v>
+        <v>64.2</v>
       </c>
       <c r="C56">
-        <v>3.4529999999999998</v>
+        <v>3.4540000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.765999999999998</v>
+        <v>63.939</v>
       </c>
       <c r="C57">
-        <v>3.4929999999999999</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>47727</v>
       </c>
       <c r="B58" s="2">
-        <v>64.698999999999998</v>
+        <v>63.701999999999998</v>
       </c>
       <c r="C58" s="2">
-        <v>3.4209999999999998</v>
+        <v>3.4660000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1105,10 +1105,10 @@
         <v>47757</v>
       </c>
       <c r="B59" s="2">
-        <v>64.600999999999999</v>
+        <v>65.352999999999994</v>
       </c>
       <c r="C59" s="2">
-        <v>3.4969999999999999</v>
+        <v>3.4660000000000002</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1116,10 +1116,10 @@
         <v>47788</v>
       </c>
       <c r="B60" s="2">
-        <v>64.430000000000007</v>
+        <v>65.096999999999994</v>
       </c>
       <c r="C60" s="2">
-        <v>3.6549999999999998</v>
+        <v>3.1360000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1127,10 +1127,10 @@
         <v>47818</v>
       </c>
       <c r="B61" s="2">
-        <v>64.233000000000004</v>
+        <v>64.790999999999997</v>
       </c>
       <c r="C61" s="2">
-        <v>4.2039999999999997</v>
+        <v>3.0960000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1138,10 +1138,10 @@
         <v>47849</v>
       </c>
       <c r="B62" s="2">
-        <v>64.069999999999993</v>
+        <v>64.484999999999999</v>
       </c>
       <c r="C62" s="2">
-        <v>4.625</v>
+        <v>3.2130000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1149,10 +1149,10 @@
         <v>47880</v>
       </c>
       <c r="B63" s="2">
-        <v>63.954999999999998</v>
+        <v>64.2</v>
       </c>
       <c r="C63" s="2">
-        <v>4.2160000000000002</v>
+        <v>3.4540000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1160,10 +1160,10 @@
         <v>47908</v>
       </c>
       <c r="B64" s="2">
-        <v>63.823</v>
+        <v>63.939</v>
       </c>
       <c r="C64" s="2">
-        <v>3.4260000000000002</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1171,10 +1171,10 @@
         <v>47939</v>
       </c>
       <c r="B65" s="2">
-        <v>63.676000000000002</v>
+        <v>63.701999999999998</v>
       </c>
       <c r="C65" s="2">
-        <v>3.052</v>
+        <v>3.4660000000000002</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,6 +1406,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1700,15 +1709,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1743,6 +1743,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1761,14 +1769,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A535F6A7-8D2F-4EDD-A686-236940F344ED}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11126D5B-CE72-4673-83AF-DA9775D9F222}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -577,10 +577,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>89.215000000000003</v>
+        <v>89.304000000000002</v>
       </c>
       <c r="C11">
-        <v>3.0065</v>
+        <v>3.0305</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +588,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>87.947999999999993</v>
+        <v>88.177999999999997</v>
       </c>
       <c r="C12">
-        <v>3.0659999999999998</v>
+        <v>3.1139999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +599,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>86.846000000000004</v>
+        <v>87.06</v>
       </c>
       <c r="C13">
-        <v>3.3580000000000001</v>
+        <v>3.4089999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +610,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>85.69</v>
+        <v>85.843999999999994</v>
       </c>
       <c r="C14">
-        <v>3.7290000000000001</v>
+        <v>3.7890000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +621,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>84.725999999999999</v>
+        <v>84.825000000000003</v>
       </c>
       <c r="C15">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +632,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>83.501999999999995</v>
+        <v>83.555999999999997</v>
       </c>
       <c r="C16">
-        <v>2.7050000000000001</v>
+        <v>2.7410000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +643,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>82.287000000000006</v>
+        <v>82.323999999999998</v>
       </c>
       <c r="C17">
-        <v>2.6179999999999999</v>
+        <v>2.6480000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +654,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>81.293999999999997</v>
+        <v>81.320999999999998</v>
       </c>
       <c r="C18">
-        <v>2.649</v>
+        <v>2.6760000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +665,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>80.302999999999997</v>
+        <v>80.313999999999993</v>
       </c>
       <c r="C19">
-        <v>2.8050000000000002</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,10 +676,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>79.260000000000005</v>
+        <v>79.245999999999995</v>
       </c>
       <c r="C20">
-        <v>3.0409999999999999</v>
+        <v>3.0630000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -687,10 +687,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>78.412999999999997</v>
+        <v>78.393000000000001</v>
       </c>
       <c r="C21">
-        <v>3.1150000000000002</v>
+        <v>3.137</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +698,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>77.557000000000002</v>
+        <v>77.540000000000006</v>
       </c>
       <c r="C22">
-        <v>3.0960000000000001</v>
+        <v>3.1179999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +709,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>76.783000000000001</v>
+        <v>76.77</v>
       </c>
       <c r="C23">
-        <v>3.1789999999999998</v>
+        <v>3.202</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>76.093000000000004</v>
+        <v>76.072999999999993</v>
       </c>
       <c r="C24">
-        <v>3.4689999999999999</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +731,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>75.364000000000004</v>
+        <v>75.346999999999994</v>
       </c>
       <c r="C25">
-        <v>4.0620000000000003</v>
+        <v>4.0949999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +742,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>74.751000000000005</v>
+        <v>74.744</v>
       </c>
       <c r="C26">
-        <v>4.4720000000000004</v>
+        <v>4.5039999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>74.248000000000005</v>
       </c>
       <c r="C27">
-        <v>4.08</v>
+        <v>4.1109999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +764,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>73.683000000000007</v>
+        <v>73.69</v>
       </c>
       <c r="C28">
-        <v>3.3719999999999999</v>
+        <v>3.391</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +775,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>73.230999999999995</v>
+        <v>73.248000000000005</v>
       </c>
       <c r="C29">
-        <v>3.165</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>72.805000000000007</v>
+        <v>72.811999999999998</v>
       </c>
       <c r="C30">
-        <v>3.1629999999999998</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +797,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>72.302000000000007</v>
+        <v>72.299000000000007</v>
       </c>
       <c r="C31">
-        <v>3.32</v>
+        <v>3.3260000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +808,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>71.89</v>
+        <v>71.884</v>
       </c>
       <c r="C32">
-        <v>3.5390000000000001</v>
+        <v>3.5409999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -822,7 +822,7 @@
         <v>71.513999999999996</v>
       </c>
       <c r="C33">
-        <v>3.5979999999999999</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +830,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>71.135000000000005</v>
+        <v>71.138000000000005</v>
       </c>
       <c r="C34">
-        <v>3.5680000000000001</v>
+        <v>3.569</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +841,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>70.814999999999998</v>
+        <v>70.825000000000003</v>
       </c>
       <c r="C35">
-        <v>3.6190000000000002</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>70.466999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="C36">
-        <v>3.7949999999999999</v>
+        <v>3.8029999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +863,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>70.087000000000003</v>
+        <v>70.111000000000004</v>
       </c>
       <c r="C37">
-        <v>4.3280000000000003</v>
+        <v>4.3410000000000002</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +874,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>69.727000000000004</v>
+        <v>69.753</v>
       </c>
       <c r="C38">
-        <v>4.7709999999999999</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +885,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>69.399000000000001</v>
+        <v>69.415999999999997</v>
       </c>
       <c r="C39">
-        <v>4.3319999999999999</v>
+        <v>4.3410000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +896,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>69.08</v>
+        <v>69.093000000000004</v>
       </c>
       <c r="C40">
-        <v>3.4039999999999999</v>
+        <v>3.4129999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>68.786000000000001</v>
+        <v>68.808999999999997</v>
       </c>
       <c r="C41">
-        <v>3.1440000000000001</v>
+        <v>3.1539999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -918,10 +918,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>68.454999999999998</v>
+        <v>68.484999999999999</v>
       </c>
       <c r="C42">
-        <v>3.1280000000000001</v>
+        <v>3.1379999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -929,10 +929,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>68.087999999999994</v>
+        <v>68.114999999999995</v>
       </c>
       <c r="C43">
-        <v>3.2509999999999999</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,10 +940,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.772999999999996</v>
+        <v>67.796999999999997</v>
       </c>
       <c r="C44">
-        <v>3.4630000000000001</v>
+        <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -951,10 +951,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.456000000000003</v>
+        <v>67.486000000000004</v>
       </c>
       <c r="C45">
-        <v>3.5190000000000001</v>
+        <v>3.5289999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,10 +962,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.162000000000006</v>
+        <v>67.201999999999998</v>
       </c>
       <c r="C46">
-        <v>3.5070000000000001</v>
+        <v>3.5179999999999998</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -973,10 +973,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.855999999999995</v>
+        <v>66.918999999999997</v>
       </c>
       <c r="C47">
-        <v>3.5680000000000001</v>
+        <v>3.5790000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.510000000000005</v>
+        <v>66.584000000000003</v>
       </c>
       <c r="C48">
-        <v>3.7040000000000002</v>
+        <v>3.718</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +995,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.201999999999998</v>
+        <v>66.286000000000001</v>
       </c>
       <c r="C49">
-        <v>4.2510000000000003</v>
+        <v>4.2649999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.923000000000002</v>
+        <v>66.016999999999996</v>
       </c>
       <c r="C50">
-        <v>4.72</v>
+        <v>4.7320000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.638000000000005</v>
+        <v>65.742000000000004</v>
       </c>
       <c r="C51">
-        <v>4.3120000000000003</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1028,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.352999999999994</v>
+        <v>65.462999999999994</v>
       </c>
       <c r="C52">
-        <v>3.4660000000000002</v>
+        <v>3.476</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.096999999999994</v>
+        <v>65.209999999999994</v>
       </c>
       <c r="C53">
-        <v>3.1360000000000001</v>
+        <v>3.145</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1050,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.790999999999997</v>
+        <v>64.915000000000006</v>
       </c>
       <c r="C54">
-        <v>3.0960000000000001</v>
+        <v>3.105</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1061,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.484999999999999</v>
+        <v>64.617999999999995</v>
       </c>
       <c r="C55">
-        <v>3.2130000000000001</v>
+        <v>3.222</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1072,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.2</v>
+        <v>64.343999999999994</v>
       </c>
       <c r="C56">
-        <v>3.4540000000000002</v>
+        <v>3.4620000000000002</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1083,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>63.939</v>
+        <v>64.093000000000004</v>
       </c>
       <c r="C57">
-        <v>3.492</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>47727</v>
       </c>
       <c r="B58" s="2">
-        <v>63.701999999999998</v>
+        <v>63.862000000000002</v>
       </c>
       <c r="C58" s="2">
-        <v>3.4660000000000002</v>
+        <v>3.4740000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,12 +1406,36 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1710,42 +1734,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1770,12 +1773,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11126D5B-CE72-4673-83AF-DA9775D9F222}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A7E91B-5B27-428F-B47A-3871736EF848}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,6 +460,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
     <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -577,10 +578,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>89.304000000000002</v>
+        <v>88.456999999999994</v>
       </c>
       <c r="C11">
-        <v>3.0305</v>
+        <v>3.0750000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -588,10 +589,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>88.177999999999997</v>
+        <v>87.373000000000005</v>
       </c>
       <c r="C12">
-        <v>3.1139999999999999</v>
+        <v>3.2029999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -599,10 +600,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>87.06</v>
+        <v>86.578999999999994</v>
       </c>
       <c r="C13">
-        <v>3.4089999999999998</v>
+        <v>3.512</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -610,10 +611,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>85.843999999999994</v>
+        <v>85.674000000000007</v>
       </c>
       <c r="C14">
-        <v>3.7890000000000001</v>
+        <v>3.8980000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -621,10 +622,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>84.825000000000003</v>
+        <v>84.867000000000004</v>
       </c>
       <c r="C15">
-        <v>3.45</v>
+        <v>3.5259999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,10 +633,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>83.555999999999997</v>
+        <v>83.786000000000001</v>
       </c>
       <c r="C16">
-        <v>2.7410000000000001</v>
+        <v>2.7749999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,10 +644,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>82.323999999999998</v>
+        <v>82.637</v>
       </c>
       <c r="C17">
-        <v>2.6480000000000001</v>
+        <v>2.6659999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -654,10 +655,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>81.320999999999998</v>
+        <v>81.635000000000005</v>
       </c>
       <c r="C18">
-        <v>2.6760000000000002</v>
+        <v>2.6920000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -665,10 +666,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>80.313999999999993</v>
+        <v>80.608999999999995</v>
       </c>
       <c r="C19">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -676,7 +677,7 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>79.245999999999995</v>
+        <v>79.510000000000005</v>
       </c>
       <c r="C20">
         <v>3.0630000000000002</v>
@@ -687,10 +688,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>78.393000000000001</v>
+        <v>78.62</v>
       </c>
       <c r="C21">
-        <v>3.137</v>
+        <v>3.1360000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -698,10 +699,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>77.540000000000006</v>
+        <v>77.727000000000004</v>
       </c>
       <c r="C22">
-        <v>3.1179999999999999</v>
+        <v>3.1190000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -709,10 +710,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>76.77</v>
+        <v>76.927000000000007</v>
       </c>
       <c r="C23">
-        <v>3.202</v>
+        <v>3.2050000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -720,10 +721,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>76.072999999999993</v>
+        <v>76.213999999999999</v>
       </c>
       <c r="C24">
-        <v>3.5</v>
+        <v>3.504</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -731,10 +732,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>75.346999999999994</v>
+        <v>75.456000000000003</v>
       </c>
       <c r="C25">
-        <v>4.0949999999999998</v>
+        <v>4.109</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -742,10 +743,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>74.744</v>
+        <v>74.819999999999993</v>
       </c>
       <c r="C26">
-        <v>4.5039999999999996</v>
+        <v>4.5220000000000002</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -753,10 +754,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>74.248000000000005</v>
+        <v>74.293000000000006</v>
       </c>
       <c r="C27">
-        <v>4.1109999999999998</v>
+        <v>4.1280000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -764,10 +765,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>73.69</v>
+        <v>73.712999999999994</v>
       </c>
       <c r="C28">
-        <v>3.391</v>
+        <v>3.3929999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +776,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>73.248000000000005</v>
+        <v>73.257999999999996</v>
       </c>
       <c r="C29">
-        <v>3.173</v>
+        <v>3.1640000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -786,10 +787,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>72.811999999999998</v>
+        <v>72.822000000000003</v>
       </c>
       <c r="C30">
-        <v>3.17</v>
+        <v>3.1640000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -797,10 +798,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>72.299000000000007</v>
+        <v>72.308999999999997</v>
       </c>
       <c r="C31">
-        <v>3.3260000000000001</v>
+        <v>3.3130000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -808,10 +809,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>71.884</v>
+        <v>71.89</v>
       </c>
       <c r="C32">
-        <v>3.5409999999999999</v>
+        <v>3.5259999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -819,10 +820,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>71.513999999999996</v>
+        <v>71.510999999999996</v>
       </c>
       <c r="C33">
-        <v>3.6</v>
+        <v>3.5859999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -830,10 +831,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>71.138000000000005</v>
+        <v>71.125</v>
       </c>
       <c r="C34">
-        <v>3.569</v>
+        <v>3.556</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -841,10 +842,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>70.825000000000003</v>
+        <v>70.805000000000007</v>
       </c>
       <c r="C35">
-        <v>3.621</v>
+        <v>3.605</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,10 +853,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>70.48</v>
+        <v>70.456999999999994</v>
       </c>
       <c r="C36">
-        <v>3.8029999999999999</v>
+        <v>3.7919999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -863,10 +864,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>70.111000000000004</v>
+        <v>70.076999999999998</v>
       </c>
       <c r="C37">
-        <v>4.3410000000000002</v>
+        <v>4.3380000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -874,10 +875,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>69.753</v>
+        <v>69.709999999999994</v>
       </c>
       <c r="C38">
-        <v>4.78</v>
+        <v>4.7750000000000004</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -885,10 +886,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>69.415999999999997</v>
+        <v>69.363</v>
       </c>
       <c r="C39">
-        <v>4.3410000000000002</v>
+        <v>4.3360000000000003</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -896,10 +897,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>69.093000000000004</v>
+        <v>69.033000000000001</v>
       </c>
       <c r="C40">
-        <v>3.4129999999999998</v>
+        <v>3.4079999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -907,7 +908,7 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>68.808999999999997</v>
+        <v>68.748999999999995</v>
       </c>
       <c r="C41">
         <v>3.1539999999999999</v>
@@ -918,7 +919,7 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>68.484999999999999</v>
+        <v>68.424999999999997</v>
       </c>
       <c r="C42">
         <v>3.1379999999999999</v>
@@ -929,10 +930,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>68.114999999999995</v>
+        <v>68.055000000000007</v>
       </c>
       <c r="C43">
-        <v>3.262</v>
+        <v>3.2589999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -940,7 +941,7 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.796999999999997</v>
+        <v>67.736999999999995</v>
       </c>
       <c r="C44">
         <v>3.4740000000000002</v>
@@ -951,10 +952,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.486000000000004</v>
+        <v>67.429000000000002</v>
       </c>
       <c r="C45">
-        <v>3.5289999999999999</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -962,7 +963,7 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.201999999999998</v>
+        <v>67.155000000000001</v>
       </c>
       <c r="C46">
         <v>3.5179999999999998</v>
@@ -973,10 +974,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.918999999999997</v>
+        <v>66.882000000000005</v>
       </c>
       <c r="C47">
-        <v>3.5790000000000002</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -984,10 +985,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.584000000000003</v>
+        <v>66.554000000000002</v>
       </c>
       <c r="C48">
-        <v>3.718</v>
+        <v>3.7210000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -995,10 +996,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.286000000000001</v>
+        <v>66.256</v>
       </c>
       <c r="C49">
-        <v>4.2649999999999997</v>
+        <v>4.2690000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1006,10 +1007,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.016999999999996</v>
+        <v>65.986999999999995</v>
       </c>
       <c r="C50">
-        <v>4.7320000000000002</v>
+        <v>4.7370000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1017,10 +1018,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.742000000000004</v>
+        <v>65.712000000000003</v>
       </c>
       <c r="C51">
-        <v>4.32</v>
+        <v>4.3250000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1028,10 +1029,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.462999999999994</v>
+        <v>65.433000000000007</v>
       </c>
       <c r="C52">
-        <v>3.476</v>
+        <v>3.4820000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1039,10 +1040,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.209999999999994</v>
+        <v>65.180000000000007</v>
       </c>
       <c r="C53">
-        <v>3.145</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1050,10 +1051,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.915000000000006</v>
+        <v>64.885000000000005</v>
       </c>
       <c r="C54">
-        <v>3.105</v>
+        <v>3.1110000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1061,10 +1062,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.617999999999995</v>
+        <v>64.584999999999994</v>
       </c>
       <c r="C55">
-        <v>3.222</v>
+        <v>3.2290000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1072,10 +1073,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.343999999999994</v>
+        <v>64.304000000000002</v>
       </c>
       <c r="C56">
-        <v>3.4620000000000002</v>
+        <v>3.4689999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1083,10 +1084,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.093000000000004</v>
+        <v>64.052999999999997</v>
       </c>
       <c r="C57">
-        <v>3.5</v>
+        <v>3.5070000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1094,10 +1095,10 @@
         <v>47727</v>
       </c>
       <c r="B58" s="2">
-        <v>63.862000000000002</v>
+        <v>63.822000000000003</v>
       </c>
       <c r="C58" s="2">
-        <v>3.4740000000000002</v>
+        <v>3.4820000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9A7E91B-5B27-428F-B47A-3871736EF848}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943CB95E-08A5-4BF6-942C-D3D7AAC2D3B6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,10 +578,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>88.456999999999994</v>
+        <v>92.433000000000007</v>
       </c>
       <c r="C11">
-        <v>3.0750000000000002</v>
+        <v>3.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -589,10 +589,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>87.373000000000005</v>
+        <v>92.61</v>
       </c>
       <c r="C12">
-        <v>3.2029999999999998</v>
+        <v>3.1669999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -600,10 +600,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>86.578999999999994</v>
+        <v>91.494</v>
       </c>
       <c r="C13">
-        <v>3.512</v>
+        <v>3.5059999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,10 +611,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>85.674000000000007</v>
+        <v>90.272000000000006</v>
       </c>
       <c r="C14">
-        <v>3.8980000000000001</v>
+        <v>3.9319999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -622,10 +622,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>84.867000000000004</v>
+        <v>89.265000000000001</v>
       </c>
       <c r="C15">
-        <v>3.5259999999999998</v>
+        <v>3.5529999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -633,10 +633,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>83.786000000000001</v>
+        <v>87.974999999999994</v>
       </c>
       <c r="C16">
-        <v>2.7749999999999999</v>
+        <v>2.7879999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -644,10 +644,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>82.637</v>
+        <v>86.617999999999995</v>
       </c>
       <c r="C17">
-        <v>2.6659999999999999</v>
+        <v>2.6850000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -655,10 +655,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>81.635000000000005</v>
+        <v>85.426000000000002</v>
       </c>
       <c r="C18">
-        <v>2.6920000000000002</v>
+        <v>2.7170000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -666,10 +666,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>80.608999999999995</v>
+        <v>84.161000000000001</v>
       </c>
       <c r="C19">
-        <v>2.84</v>
+        <v>2.871</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -677,10 +677,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>79.510000000000005</v>
+        <v>82.763999999999996</v>
       </c>
       <c r="C20">
-        <v>3.0630000000000002</v>
+        <v>3.0990000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,10 +688,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>78.62</v>
+        <v>81.611000000000004</v>
       </c>
       <c r="C21">
-        <v>3.1360000000000001</v>
+        <v>3.1709999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,10 +699,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>77.727000000000004</v>
+        <v>80.44</v>
       </c>
       <c r="C22">
-        <v>3.1190000000000002</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -710,10 +710,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>76.927000000000007</v>
+        <v>79.387</v>
       </c>
       <c r="C23">
-        <v>3.2050000000000001</v>
+        <v>3.2480000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -721,10 +721,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>76.213999999999999</v>
+        <v>78.456999999999994</v>
       </c>
       <c r="C24">
-        <v>3.504</v>
+        <v>3.5739999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -732,10 +732,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>75.456000000000003</v>
+        <v>77.491</v>
       </c>
       <c r="C25">
-        <v>4.109</v>
+        <v>4.1920000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -743,10 +743,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>74.819999999999993</v>
+        <v>76.691000000000003</v>
       </c>
       <c r="C26">
-        <v>4.5220000000000002</v>
+        <v>4.6079999999999997</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -754,10 +754,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>74.293000000000006</v>
+        <v>76.043000000000006</v>
       </c>
       <c r="C27">
-        <v>4.1280000000000001</v>
+        <v>4.1970000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -765,10 +765,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>73.712999999999994</v>
+        <v>75.334999999999994</v>
       </c>
       <c r="C28">
-        <v>3.3929999999999998</v>
+        <v>3.4239999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -776,10 +776,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>73.257999999999996</v>
+        <v>74.783000000000001</v>
       </c>
       <c r="C29">
-        <v>3.1640000000000001</v>
+        <v>3.1909999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -787,10 +787,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>72.822000000000003</v>
+        <v>74.272999999999996</v>
       </c>
       <c r="C30">
-        <v>3.1640000000000001</v>
+        <v>3.194</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,10 +798,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>72.308999999999997</v>
+        <v>73.682000000000002</v>
       </c>
       <c r="C31">
-        <v>3.3130000000000002</v>
+        <v>3.339</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -809,10 +809,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>71.89</v>
+        <v>73.195999999999998</v>
       </c>
       <c r="C32">
-        <v>3.5259999999999998</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -820,10 +820,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>71.510999999999996</v>
+        <v>72.759</v>
       </c>
       <c r="C33">
-        <v>3.5859999999999999</v>
+        <v>3.5960000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -831,10 +831,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>71.125</v>
+        <v>72.326999999999998</v>
       </c>
       <c r="C34">
-        <v>3.556</v>
+        <v>3.5670000000000002</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -842,10 +842,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>70.805000000000007</v>
+        <v>71.956000000000003</v>
       </c>
       <c r="C35">
-        <v>3.605</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -853,10 +853,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>70.456999999999994</v>
+        <v>71.55</v>
       </c>
       <c r="C36">
-        <v>3.7919999999999998</v>
+        <v>3.8210000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -864,10 +864,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>70.076999999999998</v>
+        <v>71.126999999999995</v>
       </c>
       <c r="C37">
-        <v>4.3380000000000001</v>
+        <v>4.3819999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -875,10 +875,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>69.709999999999994</v>
+        <v>70.727000000000004</v>
       </c>
       <c r="C38">
-        <v>4.7750000000000004</v>
+        <v>4.8090000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -886,10 +886,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>69.363</v>
+        <v>70.34</v>
       </c>
       <c r="C39">
-        <v>4.3360000000000003</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -897,10 +897,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>69.033000000000001</v>
+        <v>69.959999999999994</v>
       </c>
       <c r="C40">
-        <v>3.4079999999999999</v>
+        <v>3.4369999999999998</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -908,10 +908,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>68.748999999999995</v>
+        <v>69.611000000000004</v>
       </c>
       <c r="C41">
-        <v>3.1539999999999999</v>
+        <v>3.1869999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -919,10 +919,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>68.424999999999997</v>
+        <v>69.230999999999995</v>
       </c>
       <c r="C42">
-        <v>3.1379999999999999</v>
+        <v>3.1720000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -930,10 +930,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>68.055000000000007</v>
+        <v>68.804000000000002</v>
       </c>
       <c r="C43">
-        <v>3.2589999999999999</v>
+        <v>3.2869999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -941,10 +941,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>67.736999999999995</v>
+        <v>68.430000000000007</v>
       </c>
       <c r="C44">
-        <v>3.4740000000000002</v>
+        <v>3.488</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,10 +952,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>67.429000000000002</v>
+        <v>68.067999999999998</v>
       </c>
       <c r="C45">
-        <v>3.53</v>
+        <v>3.5449999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -963,10 +963,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.155000000000001</v>
+        <v>67.733000000000004</v>
       </c>
       <c r="C46">
-        <v>3.5179999999999998</v>
+        <v>3.5329999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -974,10 +974,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>66.882000000000005</v>
+        <v>67.397000000000006</v>
       </c>
       <c r="C47">
-        <v>3.58</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,10 +985,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>66.554000000000002</v>
+        <v>67.019000000000005</v>
       </c>
       <c r="C48">
-        <v>3.7210000000000001</v>
+        <v>3.7480000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,10 +996,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.256</v>
+        <v>66.688999999999993</v>
       </c>
       <c r="C49">
-        <v>4.2690000000000001</v>
+        <v>4.3019999999999996</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,10 +1007,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>65.986999999999995</v>
+        <v>66.387</v>
       </c>
       <c r="C50">
-        <v>4.7370000000000001</v>
+        <v>4.7590000000000003</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1018,10 +1018,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>65.712000000000003</v>
+        <v>66.058999999999997</v>
       </c>
       <c r="C51">
-        <v>4.3250000000000002</v>
+        <v>4.3449999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,10 +1029,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.433000000000007</v>
+        <v>65.747</v>
       </c>
       <c r="C52">
-        <v>3.4820000000000002</v>
+        <v>3.4969999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.180000000000007</v>
+        <v>65.465999999999994</v>
       </c>
       <c r="C53">
-        <v>3.1509999999999998</v>
+        <v>3.153</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,10 +1051,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>64.885000000000005</v>
+        <v>65.119</v>
       </c>
       <c r="C54">
-        <v>3.1110000000000002</v>
+        <v>3.1150000000000002</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1062,10 +1062,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.584999999999994</v>
+        <v>64.769000000000005</v>
       </c>
       <c r="C55">
-        <v>3.2290000000000001</v>
+        <v>3.2320000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1073,10 +1073,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.304000000000002</v>
+        <v>64.435000000000002</v>
       </c>
       <c r="C56">
-        <v>3.4689999999999999</v>
+        <v>3.472</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,21 +1084,21 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.052999999999997</v>
+        <v>64.128</v>
       </c>
       <c r="C57">
-        <v>3.5070000000000001</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>47727</v>
       </c>
-      <c r="B58" s="2">
-        <v>63.822000000000003</v>
-      </c>
-      <c r="C58" s="2">
-        <v>3.4820000000000002</v>
+      <c r="B58">
+        <v>63.853999999999999</v>
+      </c>
+      <c r="C58">
+        <v>3.4849999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1407,36 +1407,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1735,21 +1711,42 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1774,9 +1771,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943CB95E-08A5-4BF6-942C-D3D7AAC2D3B6}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1DABD2-263E-46CC-8671-E768B79D53E8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
   <si>
     <t>oil_price</t>
   </si>
@@ -42,6 +43,33 @@
   </si>
   <si>
     <t>gas_price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>WTI</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>SourceWTI</t>
+  </si>
+  <si>
+    <t>SourceHH</t>
+  </si>
+  <si>
+    <t>MaxAsOfDate</t>
+  </si>
+  <si>
+    <t>SETTLED</t>
+  </si>
+  <si>
+    <t>STRIP</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -79,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -94,6 +122,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,10 +607,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>92.433000000000007</v>
+        <v>92.655000000000001</v>
       </c>
       <c r="C11">
-        <v>3.0569999999999999</v>
+        <v>3.1150000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -589,10 +618,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>92.61</v>
+        <v>92.935000000000002</v>
       </c>
       <c r="C12">
-        <v>3.1669999999999998</v>
+        <v>3.2829999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -600,10 +629,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>91.494</v>
+        <v>91.885999999999996</v>
       </c>
       <c r="C13">
-        <v>3.5059999999999998</v>
+        <v>3.6019999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,10 +640,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>90.272000000000006</v>
+        <v>90.745000000000005</v>
       </c>
       <c r="C14">
-        <v>3.9319999999999999</v>
+        <v>3.9910000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -622,10 +651,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>89.265000000000001</v>
+        <v>89.81</v>
       </c>
       <c r="C15">
-        <v>3.5529999999999999</v>
+        <v>3.6030000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -633,10 +662,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>87.974999999999994</v>
+        <v>88.602000000000004</v>
       </c>
       <c r="C16">
-        <v>2.7879999999999998</v>
+        <v>2.8050000000000002</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -644,10 +673,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>86.617999999999995</v>
+        <v>87.350999999999999</v>
       </c>
       <c r="C17">
-        <v>2.6850000000000001</v>
+        <v>2.6970000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -655,10 +684,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>85.426000000000002</v>
+        <v>86.242999999999995</v>
       </c>
       <c r="C18">
-        <v>2.7170000000000001</v>
+        <v>2.7240000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -666,10 +695,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>84.161000000000001</v>
+        <v>85.063999999999993</v>
       </c>
       <c r="C19">
-        <v>2.871</v>
+        <v>2.8740000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -677,10 +706,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>82.763999999999996</v>
+        <v>83.75</v>
       </c>
       <c r="C20">
-        <v>3.0990000000000002</v>
+        <v>3.101</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -688,10 +717,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>81.611000000000004</v>
+        <v>82.653999999999996</v>
       </c>
       <c r="C21">
-        <v>3.1709999999999998</v>
+        <v>3.173</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -699,10 +728,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>80.44</v>
+        <v>81.516999999999996</v>
       </c>
       <c r="C22">
-        <v>3.157</v>
+        <v>3.1589999999999998</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -710,7 +739,7 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>79.387</v>
+        <v>80.48</v>
       </c>
       <c r="C23">
         <v>3.2480000000000002</v>
@@ -721,10 +750,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>78.456999999999994</v>
+        <v>79.557000000000002</v>
       </c>
       <c r="C24">
-        <v>3.5739999999999998</v>
+        <v>3.5710000000000002</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -732,10 +761,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>77.491</v>
+        <v>78.590999999999994</v>
       </c>
       <c r="C25">
-        <v>4.1920000000000002</v>
+        <v>4.1890000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -743,10 +772,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>76.691000000000003</v>
+        <v>77.790999999999997</v>
       </c>
       <c r="C26">
-        <v>4.6079999999999997</v>
+        <v>4.6100000000000003</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -754,10 +783,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>76.043000000000006</v>
+        <v>77.138000000000005</v>
       </c>
       <c r="C27">
-        <v>4.1970000000000001</v>
+        <v>4.1980000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -765,10 +794,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>75.334999999999994</v>
+        <v>76.408000000000001</v>
       </c>
       <c r="C28">
-        <v>3.4239999999999999</v>
+        <v>3.411</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -776,10 +805,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>74.783000000000001</v>
+        <v>75.832999999999998</v>
       </c>
       <c r="C29">
-        <v>3.1909999999999998</v>
+        <v>3.181</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -787,10 +816,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>74.272999999999996</v>
+        <v>75.295000000000002</v>
       </c>
       <c r="C30">
-        <v>3.194</v>
+        <v>3.1859999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -798,10 +827,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>73.682000000000002</v>
+        <v>74.677999999999997</v>
       </c>
       <c r="C31">
-        <v>3.339</v>
+        <v>3.3319999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -809,10 +838,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>73.195999999999998</v>
+        <v>74.174999999999997</v>
       </c>
       <c r="C32">
-        <v>3.54</v>
+        <v>3.5339999999999998</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -820,10 +849,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>72.759</v>
+        <v>73.709999999999994</v>
       </c>
       <c r="C33">
-        <v>3.5960000000000001</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -831,10 +860,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>72.326999999999998</v>
+        <v>73.247</v>
       </c>
       <c r="C34">
-        <v>3.5670000000000002</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -842,10 +871,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>71.956000000000003</v>
+        <v>72.849999999999994</v>
       </c>
       <c r="C35">
-        <v>3.621</v>
+        <v>3.6139999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -853,10 +882,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>71.55</v>
+        <v>72.423000000000002</v>
       </c>
       <c r="C36">
-        <v>3.8210000000000002</v>
+        <v>3.8109999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -864,10 +893,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>71.126999999999995</v>
+        <v>71.98</v>
       </c>
       <c r="C37">
-        <v>4.3819999999999997</v>
+        <v>4.3719999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -875,10 +904,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>70.727000000000004</v>
+        <v>71.56</v>
       </c>
       <c r="C38">
-        <v>4.8090000000000002</v>
+        <v>4.7990000000000004</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -886,10 +915,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>70.34</v>
+        <v>71.153999999999996</v>
       </c>
       <c r="C39">
-        <v>4.37</v>
+        <v>4.351</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -897,10 +926,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>69.959999999999994</v>
+        <v>70.753</v>
       </c>
       <c r="C40">
-        <v>3.4369999999999998</v>
+        <v>3.4180000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -908,10 +937,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>69.611000000000004</v>
+        <v>70.385999999999996</v>
       </c>
       <c r="C41">
-        <v>3.1869999999999998</v>
+        <v>3.1680000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -919,10 +948,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>69.230999999999995</v>
+        <v>69.984999999999999</v>
       </c>
       <c r="C42">
-        <v>3.1720000000000002</v>
+        <v>3.1549999999999998</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -930,10 +959,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>68.804000000000002</v>
+        <v>69.543999999999997</v>
       </c>
       <c r="C43">
-        <v>3.2869999999999999</v>
+        <v>3.2690000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -941,10 +970,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>68.430000000000007</v>
+        <v>69.162999999999997</v>
       </c>
       <c r="C44">
-        <v>3.488</v>
+        <v>3.464</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -952,10 +981,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>68.067999999999998</v>
+        <v>68.781000000000006</v>
       </c>
       <c r="C45">
-        <v>3.5449999999999999</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -963,10 +992,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>67.733000000000004</v>
+        <v>68.433000000000007</v>
       </c>
       <c r="C46">
-        <v>3.5329999999999999</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -974,10 +1003,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>67.397000000000006</v>
+        <v>68.09</v>
       </c>
       <c r="C47">
-        <v>3.601</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -985,10 +1014,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>67.019000000000005</v>
+        <v>67.688000000000002</v>
       </c>
       <c r="C48">
-        <v>3.7480000000000002</v>
+        <v>3.7290000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,10 +1025,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.688999999999993</v>
+        <v>67.325000000000003</v>
       </c>
       <c r="C49">
-        <v>4.3019999999999996</v>
+        <v>4.2830000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1007,10 +1036,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.387</v>
+        <v>66.992999999999995</v>
       </c>
       <c r="C50">
-        <v>4.7590000000000003</v>
+        <v>4.7409999999999997</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1018,10 +1047,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.058999999999997</v>
+        <v>66.649000000000001</v>
       </c>
       <c r="C51">
-        <v>4.3449999999999998</v>
+        <v>4.327</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1029,10 +1058,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.747</v>
+        <v>66.31</v>
       </c>
       <c r="C52">
-        <v>3.4969999999999999</v>
+        <v>3.4790000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1040,10 +1069,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.465999999999994</v>
+        <v>66.007000000000005</v>
       </c>
       <c r="C53">
-        <v>3.153</v>
+        <v>3.1349999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1051,10 +1080,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.119</v>
+        <v>65.629000000000005</v>
       </c>
       <c r="C54">
-        <v>3.1150000000000002</v>
+        <v>3.097</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1062,10 +1091,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.769000000000005</v>
+        <v>65.263000000000005</v>
       </c>
       <c r="C55">
-        <v>3.2320000000000002</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1073,10 +1102,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.435000000000002</v>
+        <v>64.935000000000002</v>
       </c>
       <c r="C56">
-        <v>3.472</v>
+        <v>3.4550000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1084,10 +1113,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.128</v>
+        <v>64.625</v>
       </c>
       <c r="C57">
-        <v>3.51</v>
+        <v>3.4929999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1095,10 +1124,10 @@
         <v>47727</v>
       </c>
       <c r="B58">
-        <v>63.853999999999999</v>
+        <v>64.340999999999994</v>
       </c>
       <c r="C58">
-        <v>3.4849999999999999</v>
+        <v>3.468</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1406,16 +1435,1237 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{664424DC-87FE-407A-99E4-0B6D25C8DBE9}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B2">
+        <v>60.07</v>
+      </c>
+      <c r="C2">
+        <v>3.1211000000000002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B3">
+        <v>59.478999999999999</v>
+      </c>
+      <c r="C3">
+        <v>3.7837999999999998</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B4">
+        <v>57.866</v>
+      </c>
+      <c r="C4">
+        <v>4.1501999999999999</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B5">
+        <v>60.26</v>
+      </c>
+      <c r="C5">
+        <v>7.7126000000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B6">
+        <v>64.522999999999996</v>
+      </c>
+      <c r="C6">
+        <v>3.8382000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B7">
+        <v>90.997</v>
+      </c>
+      <c r="C7">
+        <v>3.0581999999999998</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B8">
+        <v>98.06</v>
+      </c>
+      <c r="C8">
+        <v>2.7736999999999998</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B9">
+        <v>98.513999999999996</v>
+      </c>
+      <c r="C9">
+        <v>2.8881999999999999</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B10">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="C10">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B11">
+        <v>79.22</v>
+      </c>
+      <c r="C11">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B12">
+        <v>82.451999999999998</v>
+      </c>
+      <c r="C12">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B13">
+        <v>95.686999999999998</v>
+      </c>
+      <c r="C13">
+        <v>2.9470000000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B14">
+        <v>92.655000000000001</v>
+      </c>
+      <c r="C14">
+        <v>3.1150000000000002</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46327</v>
+      </c>
+      <c r="B15">
+        <v>92.935000000000002</v>
+      </c>
+      <c r="C15">
+        <v>3.2829999999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>46357</v>
+      </c>
+      <c r="B16">
+        <v>91.885999999999996</v>
+      </c>
+      <c r="C16">
+        <v>3.6019999999999999</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46388</v>
+      </c>
+      <c r="B17">
+        <v>90.745000000000005</v>
+      </c>
+      <c r="C17">
+        <v>3.9910000000000001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46419</v>
+      </c>
+      <c r="B18">
+        <v>89.81</v>
+      </c>
+      <c r="C18">
+        <v>3.6030000000000002</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46447</v>
+      </c>
+      <c r="B19">
+        <v>88.602000000000004</v>
+      </c>
+      <c r="C19">
+        <v>2.8050000000000002</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46478</v>
+      </c>
+      <c r="B20">
+        <v>87.350999999999999</v>
+      </c>
+      <c r="C20">
+        <v>2.6970000000000001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46508</v>
+      </c>
+      <c r="B21">
+        <v>86.242999999999995</v>
+      </c>
+      <c r="C21">
+        <v>2.7240000000000002</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46539</v>
+      </c>
+      <c r="B22">
+        <v>85.063999999999993</v>
+      </c>
+      <c r="C22">
+        <v>2.8740000000000001</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>46569</v>
+      </c>
+      <c r="B23">
+        <v>83.75</v>
+      </c>
+      <c r="C23">
+        <v>3.101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>46600</v>
+      </c>
+      <c r="B24">
+        <v>82.653999999999996</v>
+      </c>
+      <c r="C24">
+        <v>3.173</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>46631</v>
+      </c>
+      <c r="B25">
+        <v>81.516999999999996</v>
+      </c>
+      <c r="C25">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46661</v>
+      </c>
+      <c r="B26">
+        <v>80.48</v>
+      </c>
+      <c r="C26">
+        <v>3.2480000000000002</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46692</v>
+      </c>
+      <c r="B27">
+        <v>79.557000000000002</v>
+      </c>
+      <c r="C27">
+        <v>3.5710000000000002</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46722</v>
+      </c>
+      <c r="B28">
+        <v>78.590999999999994</v>
+      </c>
+      <c r="C28">
+        <v>4.1890000000000001</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>46753</v>
+      </c>
+      <c r="B29">
+        <v>77.790999999999997</v>
+      </c>
+      <c r="C29">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>46784</v>
+      </c>
+      <c r="B30">
+        <v>77.138000000000005</v>
+      </c>
+      <c r="C30">
+        <v>4.1980000000000004</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46813</v>
+      </c>
+      <c r="B31">
+        <v>76.408000000000001</v>
+      </c>
+      <c r="C31">
+        <v>3.411</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>46844</v>
+      </c>
+      <c r="B32">
+        <v>75.832999999999998</v>
+      </c>
+      <c r="C32">
+        <v>3.181</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>46874</v>
+      </c>
+      <c r="B33">
+        <v>75.295000000000002</v>
+      </c>
+      <c r="C33">
+        <v>3.1859999999999999</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>46905</v>
+      </c>
+      <c r="B34">
+        <v>74.677999999999997</v>
+      </c>
+      <c r="C34">
+        <v>3.3319999999999999</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>46935</v>
+      </c>
+      <c r="B35">
+        <v>74.174999999999997</v>
+      </c>
+      <c r="C35">
+        <v>3.5339999999999998</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46966</v>
+      </c>
+      <c r="B36">
+        <v>73.709999999999994</v>
+      </c>
+      <c r="C36">
+        <v>3.59</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>46997</v>
+      </c>
+      <c r="B37">
+        <v>73.247</v>
+      </c>
+      <c r="C37">
+        <v>3.56</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>47027</v>
+      </c>
+      <c r="B38">
+        <v>72.849999999999994</v>
+      </c>
+      <c r="C38">
+        <v>3.6139999999999999</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>47058</v>
+      </c>
+      <c r="B39">
+        <v>72.423000000000002</v>
+      </c>
+      <c r="C39">
+        <v>3.8109999999999999</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>47088</v>
+      </c>
+      <c r="B40">
+        <v>71.98</v>
+      </c>
+      <c r="C40">
+        <v>4.3719999999999999</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>47119</v>
+      </c>
+      <c r="B41">
+        <v>71.56</v>
+      </c>
+      <c r="C41">
+        <v>4.7990000000000004</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>47150</v>
+      </c>
+      <c r="B42">
+        <v>71.153999999999996</v>
+      </c>
+      <c r="C42">
+        <v>4.351</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>47178</v>
+      </c>
+      <c r="B43">
+        <v>70.753</v>
+      </c>
+      <c r="C43">
+        <v>3.4180000000000001</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>47209</v>
+      </c>
+      <c r="B44">
+        <v>70.385999999999996</v>
+      </c>
+      <c r="C44">
+        <v>3.1680000000000001</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>47239</v>
+      </c>
+      <c r="B45">
+        <v>69.984999999999999</v>
+      </c>
+      <c r="C45">
+        <v>3.1549999999999998</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>47270</v>
+      </c>
+      <c r="B46">
+        <v>69.543999999999997</v>
+      </c>
+      <c r="C46">
+        <v>3.2690000000000001</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>47300</v>
+      </c>
+      <c r="B47">
+        <v>69.162999999999997</v>
+      </c>
+      <c r="C47">
+        <v>3.464</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47331</v>
+      </c>
+      <c r="B48">
+        <v>68.781000000000006</v>
+      </c>
+      <c r="C48">
+        <v>3.52</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47362</v>
+      </c>
+      <c r="B49">
+        <v>68.433000000000007</v>
+      </c>
+      <c r="C49">
+        <v>3.51</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>47392</v>
+      </c>
+      <c r="B50">
+        <v>68.09</v>
+      </c>
+      <c r="C50">
+        <v>3.58</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47423</v>
+      </c>
+      <c r="B51">
+        <v>67.688000000000002</v>
+      </c>
+      <c r="C51">
+        <v>3.7290000000000001</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>47453</v>
+      </c>
+      <c r="B52">
+        <v>67.325000000000003</v>
+      </c>
+      <c r="C52">
+        <v>4.2830000000000004</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>47484</v>
+      </c>
+      <c r="B53">
+        <v>66.992999999999995</v>
+      </c>
+      <c r="C53">
+        <v>4.7409999999999997</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>47515</v>
+      </c>
+      <c r="B54">
+        <v>66.649000000000001</v>
+      </c>
+      <c r="C54">
+        <v>4.327</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>47543</v>
+      </c>
+      <c r="B55">
+        <v>66.31</v>
+      </c>
+      <c r="C55">
+        <v>3.4790000000000001</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>47574</v>
+      </c>
+      <c r="B56">
+        <v>66.007000000000005</v>
+      </c>
+      <c r="C56">
+        <v>3.1349999999999998</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>47604</v>
+      </c>
+      <c r="B57">
+        <v>65.629000000000005</v>
+      </c>
+      <c r="C57">
+        <v>3.097</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>47635</v>
+      </c>
+      <c r="B58">
+        <v>65.263000000000005</v>
+      </c>
+      <c r="C58">
+        <v>3.214</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>47665</v>
+      </c>
+      <c r="B59">
+        <v>64.935000000000002</v>
+      </c>
+      <c r="C59">
+        <v>3.4550000000000001</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>47696</v>
+      </c>
+      <c r="B60">
+        <v>64.625</v>
+      </c>
+      <c r="C60">
+        <v>3.4929999999999999</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>47727</v>
+      </c>
+      <c r="B61">
+        <v>64.340999999999994</v>
+      </c>
+      <c r="C61">
+        <v>3.468</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -1710,6 +2960,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1744,14 +3003,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1770,6 +3021,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>

--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="141" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{476A6A60-08E3-4E7D-ADCA-7E6C01C8F0E5}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44ABD489-F267-437D-923B-A796769F4063}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
   <si>
     <t>oil_price</t>
   </si>
@@ -42,6 +43,33 @@
   </si>
   <si>
     <t>gas_price</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>WTI</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>SourceWTI</t>
+  </si>
+  <si>
+    <t>SourceHH</t>
+  </si>
+  <si>
+    <t>MaxAsOfDate</t>
+  </si>
+  <si>
+    <t>SETTLED</t>
+  </si>
+  <si>
+    <t>STRIP</t>
+  </si>
+  <si>
+    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -79,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -94,6 +122,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,14 +485,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C85"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="5" customWidth="1"/>
-    <col min="2" max="3" width="12.7265625" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" style="5" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -474,7 +503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>46023</v>
       </c>
@@ -485,7 +514,7 @@
         <v>4.6870000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
@@ -496,7 +525,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>46082</v>
       </c>
@@ -507,7 +536,7 @@
         <v>2.9689999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>46113</v>
       </c>
@@ -518,7 +547,7 @@
         <v>3.0950000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>46143</v>
       </c>
@@ -529,7 +558,7 @@
         <v>2.8881999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>46174</v>
       </c>
@@ -540,7 +569,7 @@
         <v>3.1429999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46204</v>
       </c>
@@ -551,7 +580,7 @@
         <v>2.9386999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>46235</v>
       </c>
@@ -562,7 +591,7 @@
         <v>2.7410000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>46266</v>
       </c>
@@ -573,535 +602,535 @@
         <v>2.9470000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>93.135999999999996</v>
+        <v>95.991</v>
       </c>
       <c r="C11">
-        <v>3.0724999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.0314999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>93.632999999999996</v>
+        <v>98.625</v>
       </c>
       <c r="C12">
-        <v>3.198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1160000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>92.415999999999997</v>
+        <v>96.816000000000003</v>
       </c>
       <c r="C13">
-        <v>3.5590000000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.3860000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>91.033000000000001</v>
+        <v>94.762</v>
       </c>
       <c r="C14">
-        <v>3.9729999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.7589999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>89.903999999999996</v>
+        <v>93.150999999999996</v>
       </c>
       <c r="C15">
-        <v>3.5880000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.3860000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>88.528999999999996</v>
+        <v>91.283000000000001</v>
       </c>
       <c r="C16">
-        <v>2.7970000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2.6469999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>87.176000000000002</v>
+        <v>89.537000000000006</v>
       </c>
       <c r="C17">
-        <v>2.694</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2.5640000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>86.04</v>
+        <v>88.12</v>
       </c>
       <c r="C18">
-        <v>2.722</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2.6019999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>84.856999999999999</v>
+        <v>86.647000000000006</v>
       </c>
       <c r="C19">
-        <v>2.8719999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2.7639999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>83.55</v>
+        <v>85.049000000000007</v>
       </c>
       <c r="C20">
-        <v>3.0990000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.0049999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>82.463999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="C21">
-        <v>3.1709999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>81.352999999999994</v>
+        <v>82.447000000000003</v>
       </c>
       <c r="C22">
-        <v>3.157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.0649999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>80.326999999999998</v>
+        <v>81.272999999999996</v>
       </c>
       <c r="C23">
-        <v>3.2480000000000002</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1520000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>79.391000000000005</v>
+        <v>80.242999999999995</v>
       </c>
       <c r="C24">
-        <v>3.5739999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.4710000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>78.406999999999996</v>
+        <v>79.162000000000006</v>
       </c>
       <c r="C25">
-        <v>4.2009999999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.1029999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>77.593999999999994</v>
+        <v>78.283000000000001</v>
       </c>
       <c r="C26">
-        <v>4.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.5270000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>76.930000000000007</v>
+        <v>77.564999999999998</v>
       </c>
       <c r="C27">
-        <v>4.2130000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.1390000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>76.203999999999994</v>
+        <v>76.784000000000006</v>
       </c>
       <c r="C28">
-        <v>3.4220000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.3650000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>75.62</v>
+        <v>76.174000000000007</v>
       </c>
       <c r="C29">
-        <v>3.1890000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1509999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>75.072000000000003</v>
+        <v>75.611999999999995</v>
       </c>
       <c r="C30">
-        <v>3.1949999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1589999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>74.44</v>
+        <v>74.98</v>
       </c>
       <c r="C31">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.3140000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>73.921999999999997</v>
+        <v>74.465000000000003</v>
       </c>
       <c r="C32">
-        <v>3.5379999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.5209999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>73.444000000000003</v>
+        <v>74</v>
       </c>
       <c r="C33">
-        <v>3.593</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.5779999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>72.959999999999994</v>
+        <v>73.533000000000001</v>
       </c>
       <c r="C34">
-        <v>3.5640000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>72.55</v>
+        <v>73.135999999999996</v>
       </c>
       <c r="C35">
-        <v>3.6190000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.6040000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>72.123000000000005</v>
+        <v>72.727000000000004</v>
       </c>
       <c r="C36">
-        <v>3.8140000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.8010000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>71.676000000000002</v>
+        <v>72.286000000000001</v>
       </c>
       <c r="C37">
-        <v>4.3739999999999997</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.3719999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>71.247</v>
+        <v>71.856999999999999</v>
       </c>
       <c r="C38">
-        <v>4.7939999999999996</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.7930000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>70.831000000000003</v>
+        <v>71.441000000000003</v>
       </c>
       <c r="C39">
-        <v>4.3550000000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.351</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>70.417000000000002</v>
+        <v>71.037000000000006</v>
       </c>
       <c r="C40">
-        <v>3.4159999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.4089999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>70.033000000000001</v>
+        <v>70.676000000000002</v>
       </c>
       <c r="C41">
-        <v>3.1619999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1549999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>69.623000000000005</v>
+        <v>70.275000000000006</v>
       </c>
       <c r="C42">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1419999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>69.174000000000007</v>
+        <v>69.826999999999998</v>
       </c>
       <c r="C43">
-        <v>3.2650000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.2559999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>68.8</v>
+        <v>69.436999999999998</v>
       </c>
       <c r="C44">
-        <v>3.4620000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.452</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>68.435000000000002</v>
+        <v>69.061000000000007</v>
       </c>
       <c r="C45">
-        <v>3.5169999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.5059999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>68.085999999999999</v>
+        <v>68.712999999999994</v>
       </c>
       <c r="C46">
-        <v>3.5070000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.4969999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>67.73</v>
+        <v>68.367000000000004</v>
       </c>
       <c r="C47">
-        <v>3.5750000000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.5659999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>67.331000000000003</v>
+        <v>67.95</v>
       </c>
       <c r="C48">
-        <v>3.726</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.7170000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>66.968000000000004</v>
+        <v>67.584999999999994</v>
       </c>
       <c r="C49">
-        <v>4.282</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.2729999999999997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>66.623000000000005</v>
+        <v>67.27</v>
       </c>
       <c r="C50">
-        <v>4.7370000000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.278999999999996</v>
+        <v>66.923000000000002</v>
       </c>
       <c r="C51">
-        <v>4.319</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>65.936999999999998</v>
+        <v>66.587000000000003</v>
       </c>
       <c r="C52">
-        <v>3.4729999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.4769999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>65.623999999999995</v>
+        <v>66.277000000000001</v>
       </c>
       <c r="C53">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1379999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.236000000000004</v>
+        <v>65.899000000000001</v>
       </c>
       <c r="C54">
-        <v>3.097</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.1080000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>64.869</v>
+        <v>65.539000000000001</v>
       </c>
       <c r="C55">
-        <v>3.2130000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.2250000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>64.555000000000007</v>
+        <v>65.227999999999994</v>
       </c>
       <c r="C56">
-        <v>3.4510000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.4620000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.245000000000005</v>
+        <v>64.924999999999997</v>
       </c>
       <c r="C57">
-        <v>3.4889999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>47727</v>
       </c>
       <c r="B58">
-        <v>63.963999999999999</v>
+        <v>64.653000000000006</v>
       </c>
       <c r="C58">
-        <v>3.464</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+        <v>3.476</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>47757</v>
       </c>
@@ -1112,7 +1141,7 @@
         <v>3.4660000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>47788</v>
       </c>
@@ -1123,7 +1152,7 @@
         <v>3.1360000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>47818</v>
       </c>
@@ -1134,7 +1163,7 @@
         <v>3.0960000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>47849</v>
       </c>
@@ -1145,7 +1174,7 @@
         <v>3.2130000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>47880</v>
       </c>
@@ -1156,7 +1185,7 @@
         <v>3.4540000000000002</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>47908</v>
       </c>
@@ -1167,7 +1196,7 @@
         <v>3.492</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>47939</v>
       </c>
@@ -1178,7 +1207,7 @@
         <v>3.4660000000000002</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>47969</v>
       </c>
@@ -1189,7 +1218,7 @@
         <v>3.0139999999999998</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>48000</v>
       </c>
@@ -1200,7 +1229,7 @@
         <v>3.1360000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>48030</v>
       </c>
@@ -1211,7 +1240,7 @@
         <v>3.3559999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>48061</v>
       </c>
@@ -1222,7 +1251,7 @@
         <v>3.4180000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>48092</v>
       </c>
@@ -1233,7 +1262,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>48122</v>
       </c>
@@ -1244,7 +1273,7 @@
         <v>3.4860000000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>48153</v>
       </c>
@@ -1255,7 +1284,7 @@
         <v>3.7149999999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>48183</v>
       </c>
@@ -1266,7 +1295,7 @@
         <v>4.3179999999999996</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>48214</v>
       </c>
@@ -1277,7 +1306,7 @@
         <v>4.6550000000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>48245</v>
       </c>
@@ -1288,7 +1317,7 @@
         <v>4.2469999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>48274</v>
       </c>
@@ -1299,7 +1328,7 @@
         <v>3.4009999999999998</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>48305</v>
       </c>
@@ -1310,7 +1339,7 @@
         <v>2.968</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>48335</v>
       </c>
@@ -1321,7 +1350,7 @@
         <v>2.9359999999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>48366</v>
       </c>
@@ -1332,7 +1361,7 @@
         <v>3.0510000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>48396</v>
       </c>
@@ -1343,7 +1372,7 @@
         <v>3.2320000000000002</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>48427</v>
       </c>
@@ -1354,7 +1383,7 @@
         <v>3.2839999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>48458</v>
       </c>
@@ -1365,7 +1394,7 @@
         <v>3.2589999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>48488</v>
       </c>
@@ -1376,7 +1405,7 @@
         <v>3.3239999999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>48519</v>
       </c>
@@ -1387,7 +1416,7 @@
         <v>3.5390000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>48549</v>
       </c>
@@ -1406,13 +1435,1267 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FF6D68-A506-45F0-B54E-4A15775B9528}">
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B2">
+        <v>60.07</v>
+      </c>
+      <c r="C2">
+        <v>3.1211000000000002</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B3">
+        <v>59.478999999999999</v>
+      </c>
+      <c r="C3">
+        <v>3.7837999999999998</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B4">
+        <v>57.866</v>
+      </c>
+      <c r="C4">
+        <v>4.1501999999999999</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B5">
+        <v>60.26</v>
+      </c>
+      <c r="C5">
+        <v>7.7126000000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B6">
+        <v>64.522999999999996</v>
+      </c>
+      <c r="C6">
+        <v>3.8382000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B7">
+        <v>90.997</v>
+      </c>
+      <c r="C7">
+        <v>3.0581999999999998</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B8">
+        <v>98.06</v>
+      </c>
+      <c r="C8">
+        <v>2.7736999999999998</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B9">
+        <v>98.513999999999996</v>
+      </c>
+      <c r="C9">
+        <v>2.8881999999999999</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B10">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="C10">
+        <v>3.1429999999999998</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B11">
+        <v>79.22</v>
+      </c>
+      <c r="C11">
+        <v>2.9386999999999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B12">
+        <v>82.451999999999998</v>
+      </c>
+      <c r="C12">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46266</v>
+      </c>
+      <c r="B13">
+        <v>95.686999999999998</v>
+      </c>
+      <c r="C13">
+        <v>2.9470000000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B14">
+        <v>95.991</v>
+      </c>
+      <c r="C14">
+        <v>3.0314999999999999</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>46327</v>
+      </c>
+      <c r="B15">
+        <v>98.625</v>
+      </c>
+      <c r="C15">
+        <v>3.1160000000000001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>46357</v>
+      </c>
+      <c r="B16">
+        <v>96.816000000000003</v>
+      </c>
+      <c r="C16">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>46388</v>
+      </c>
+      <c r="B17">
+        <v>94.762</v>
+      </c>
+      <c r="C17">
+        <v>3.7589999999999999</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>46419</v>
+      </c>
+      <c r="B18">
+        <v>93.150999999999996</v>
+      </c>
+      <c r="C18">
+        <v>3.3860000000000001</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>46447</v>
+      </c>
+      <c r="B19">
+        <v>91.283000000000001</v>
+      </c>
+      <c r="C19">
+        <v>2.6469999999999998</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>46478</v>
+      </c>
+      <c r="B20">
+        <v>89.537000000000006</v>
+      </c>
+      <c r="C20">
+        <v>2.5640000000000001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>46508</v>
+      </c>
+      <c r="B21">
+        <v>88.12</v>
+      </c>
+      <c r="C21">
+        <v>2.6019999999999999</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>46539</v>
+      </c>
+      <c r="B22">
+        <v>86.647000000000006</v>
+      </c>
+      <c r="C22">
+        <v>2.7639999999999998</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>46569</v>
+      </c>
+      <c r="B23">
+        <v>85.049000000000007</v>
+      </c>
+      <c r="C23">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>46600</v>
+      </c>
+      <c r="B24">
+        <v>83.75</v>
+      </c>
+      <c r="C24">
+        <v>3.08</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>46631</v>
+      </c>
+      <c r="B25">
+        <v>82.447000000000003</v>
+      </c>
+      <c r="C25">
+        <v>3.0649999999999999</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46661</v>
+      </c>
+      <c r="B26">
+        <v>81.272999999999996</v>
+      </c>
+      <c r="C26">
+        <v>3.1520000000000001</v>
+      </c>
+      <c r="D26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46692</v>
+      </c>
+      <c r="B27">
+        <v>80.242999999999995</v>
+      </c>
+      <c r="C27">
+        <v>3.4710000000000001</v>
+      </c>
+      <c r="D27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46722</v>
+      </c>
+      <c r="B28">
+        <v>79.162000000000006</v>
+      </c>
+      <c r="C28">
+        <v>4.1029999999999998</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>46753</v>
+      </c>
+      <c r="B29">
+        <v>78.283000000000001</v>
+      </c>
+      <c r="C29">
+        <v>4.5270000000000001</v>
+      </c>
+      <c r="D29" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>46784</v>
+      </c>
+      <c r="B30">
+        <v>77.564999999999998</v>
+      </c>
+      <c r="C30">
+        <v>4.1390000000000002</v>
+      </c>
+      <c r="D30" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>46813</v>
+      </c>
+      <c r="B31">
+        <v>76.784000000000006</v>
+      </c>
+      <c r="C31">
+        <v>3.3650000000000002</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>46844</v>
+      </c>
+      <c r="B32">
+        <v>76.174000000000007</v>
+      </c>
+      <c r="C32">
+        <v>3.1509999999999998</v>
+      </c>
+      <c r="D32" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>46874</v>
+      </c>
+      <c r="B33">
+        <v>75.611999999999995</v>
+      </c>
+      <c r="C33">
+        <v>3.1589999999999998</v>
+      </c>
+      <c r="D33" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>46905</v>
+      </c>
+      <c r="B34">
+        <v>74.98</v>
+      </c>
+      <c r="C34">
+        <v>3.3140000000000001</v>
+      </c>
+      <c r="D34" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>46935</v>
+      </c>
+      <c r="B35">
+        <v>74.465000000000003</v>
+      </c>
+      <c r="C35">
+        <v>3.5209999999999999</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>46966</v>
+      </c>
+      <c r="B36">
+        <v>74</v>
+      </c>
+      <c r="C36">
+        <v>3.5779999999999998</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>46997</v>
+      </c>
+      <c r="B37">
+        <v>73.533000000000001</v>
+      </c>
+      <c r="C37">
+        <v>3.55</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>47027</v>
+      </c>
+      <c r="B38">
+        <v>73.135999999999996</v>
+      </c>
+      <c r="C38">
+        <v>3.6040000000000001</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>47058</v>
+      </c>
+      <c r="B39">
+        <v>72.727000000000004</v>
+      </c>
+      <c r="C39">
+        <v>3.8010000000000002</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>47088</v>
+      </c>
+      <c r="B40">
+        <v>72.286000000000001</v>
+      </c>
+      <c r="C40">
+        <v>4.3719999999999999</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>47119</v>
+      </c>
+      <c r="B41">
+        <v>71.856999999999999</v>
+      </c>
+      <c r="C41">
+        <v>4.7930000000000001</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>47150</v>
+      </c>
+      <c r="B42">
+        <v>71.441000000000003</v>
+      </c>
+      <c r="C42">
+        <v>4.351</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>47178</v>
+      </c>
+      <c r="B43">
+        <v>71.037000000000006</v>
+      </c>
+      <c r="C43">
+        <v>3.4089999999999998</v>
+      </c>
+      <c r="D43" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>47209</v>
+      </c>
+      <c r="B44">
+        <v>70.676000000000002</v>
+      </c>
+      <c r="C44">
+        <v>3.1549999999999998</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>47239</v>
+      </c>
+      <c r="B45">
+        <v>70.275000000000006</v>
+      </c>
+      <c r="C45">
+        <v>3.1419999999999999</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>47270</v>
+      </c>
+      <c r="B46">
+        <v>69.826999999999998</v>
+      </c>
+      <c r="C46">
+        <v>3.2559999999999998</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>47300</v>
+      </c>
+      <c r="B47">
+        <v>69.436999999999998</v>
+      </c>
+      <c r="C47">
+        <v>3.452</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>47331</v>
+      </c>
+      <c r="B48">
+        <v>69.061000000000007</v>
+      </c>
+      <c r="C48">
+        <v>3.5059999999999998</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>47362</v>
+      </c>
+      <c r="B49">
+        <v>68.712999999999994</v>
+      </c>
+      <c r="C49">
+        <v>3.4969999999999999</v>
+      </c>
+      <c r="D49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>47392</v>
+      </c>
+      <c r="B50">
+        <v>68.367000000000004</v>
+      </c>
+      <c r="C50">
+        <v>3.5659999999999998</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>47423</v>
+      </c>
+      <c r="B51">
+        <v>67.95</v>
+      </c>
+      <c r="C51">
+        <v>3.7170000000000001</v>
+      </c>
+      <c r="D51" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>47453</v>
+      </c>
+      <c r="B52">
+        <v>67.584999999999994</v>
+      </c>
+      <c r="C52">
+        <v>4.2729999999999997</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>47484</v>
+      </c>
+      <c r="B53">
+        <v>67.27</v>
+      </c>
+      <c r="C53">
+        <v>4.7300000000000004</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>47515</v>
+      </c>
+      <c r="B54">
+        <v>66.923000000000002</v>
+      </c>
+      <c r="C54">
+        <v>4.32</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>47543</v>
+      </c>
+      <c r="B55">
+        <v>66.587000000000003</v>
+      </c>
+      <c r="C55">
+        <v>3.4769999999999999</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>47574</v>
+      </c>
+      <c r="B56">
+        <v>66.277000000000001</v>
+      </c>
+      <c r="C56">
+        <v>3.1379999999999999</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>47604</v>
+      </c>
+      <c r="B57">
+        <v>65.899000000000001</v>
+      </c>
+      <c r="C57">
+        <v>3.1080000000000001</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>47635</v>
+      </c>
+      <c r="B58">
+        <v>65.539000000000001</v>
+      </c>
+      <c r="C58">
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>47665</v>
+      </c>
+      <c r="B59">
+        <v>65.227999999999994</v>
+      </c>
+      <c r="C59">
+        <v>3.4620000000000002</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>47696</v>
+      </c>
+      <c r="B60">
+        <v>64.924999999999997</v>
+      </c>
+      <c r="C60">
+        <v>3.5</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>47727</v>
+      </c>
+      <c r="B61">
+        <v>64.653000000000006</v>
+      </c>
+      <c r="C61">
+        <v>3.476</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" s="6">
+        <v>46311</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1711,42 +2994,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1771,12 +3033,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
-    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/price_file_library.xlsx
+++ b/price_file_library.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44ABD489-F267-437D-923B-A796769F4063}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{E1865A1F-5BD1-4F07-8E72-933E1F609FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34BE1FF0-0EA0-492F-8A11-43060B593F4A}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>oil_price</t>
   </si>
@@ -43,33 +42,6 @@
   </si>
   <si>
     <t>gas_price</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>WTI</t>
-  </si>
-  <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>SourceWTI</t>
-  </si>
-  <si>
-    <t>SourceHH</t>
-  </si>
-  <si>
-    <t>MaxAsOfDate</t>
-  </si>
-  <si>
-    <t>SETTLED</t>
-  </si>
-  <si>
-    <t>STRIP</t>
-  </si>
-  <si>
-    <t>AVG</t>
   </si>
 </sst>
 </file>
@@ -107,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -122,7 +94,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,10 +578,10 @@
         <v>46296</v>
       </c>
       <c r="B11">
-        <v>95.991</v>
+        <v>95.674000000000007</v>
       </c>
       <c r="C11">
-        <v>3.0314999999999999</v>
+        <v>2.9550000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -618,10 +589,10 @@
         <v>46327</v>
       </c>
       <c r="B12">
-        <v>98.625</v>
+        <v>97.37</v>
       </c>
       <c r="C12">
-        <v>3.1160000000000001</v>
+        <v>2.9630000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -629,10 +600,10 @@
         <v>46357</v>
       </c>
       <c r="B13">
-        <v>96.816000000000003</v>
+        <v>95.393000000000001</v>
       </c>
       <c r="C13">
-        <v>3.3860000000000001</v>
+        <v>3.3010000000000002</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -640,10 +611,10 @@
         <v>46388</v>
       </c>
       <c r="B14">
-        <v>94.762</v>
+        <v>93.361000000000004</v>
       </c>
       <c r="C14">
-        <v>3.7589999999999999</v>
+        <v>3.6909999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -651,10 +622,10 @@
         <v>46419</v>
       </c>
       <c r="B15">
-        <v>93.150999999999996</v>
+        <v>91.825999999999993</v>
       </c>
       <c r="C15">
-        <v>3.3860000000000001</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -662,10 +633,10 @@
         <v>46447</v>
       </c>
       <c r="B16">
-        <v>91.283000000000001</v>
+        <v>90.099000000000004</v>
       </c>
       <c r="C16">
-        <v>2.6469999999999998</v>
+        <v>2.617</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -673,10 +644,10 @@
         <v>46478</v>
       </c>
       <c r="B17">
-        <v>89.537000000000006</v>
+        <v>88.534999999999997</v>
       </c>
       <c r="C17">
-        <v>2.5640000000000001</v>
+        <v>2.5379999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -684,10 +655,10 @@
         <v>46508</v>
       </c>
       <c r="B18">
-        <v>88.12</v>
+        <v>87.274000000000001</v>
       </c>
       <c r="C18">
-        <v>2.6019999999999999</v>
+        <v>2.577</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -695,10 +666,10 @@
         <v>46539</v>
       </c>
       <c r="B19">
-        <v>86.647000000000006</v>
+        <v>85.99</v>
       </c>
       <c r="C19">
-        <v>2.7639999999999998</v>
+        <v>2.7360000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -706,10 +677,10 @@
         <v>46569</v>
       </c>
       <c r="B20">
-        <v>85.049000000000007</v>
+        <v>84.637</v>
       </c>
       <c r="C20">
-        <v>3.0049999999999999</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -717,10 +688,10 @@
         <v>46600</v>
       </c>
       <c r="B21">
-        <v>83.75</v>
+        <v>83.552999999999997</v>
       </c>
       <c r="C21">
-        <v>3.08</v>
+        <v>3.0550000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -728,10 +699,10 @@
         <v>46631</v>
       </c>
       <c r="B22">
-        <v>82.447000000000003</v>
+        <v>82.483000000000004</v>
       </c>
       <c r="C22">
-        <v>3.0649999999999999</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -739,10 +710,10 @@
         <v>46661</v>
       </c>
       <c r="B23">
-        <v>81.272999999999996</v>
+        <v>81.52</v>
       </c>
       <c r="C23">
-        <v>3.1520000000000001</v>
+        <v>3.1259999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -750,10 +721,10 @@
         <v>46692</v>
       </c>
       <c r="B24">
-        <v>80.242999999999995</v>
+        <v>80.64</v>
       </c>
       <c r="C24">
-        <v>3.4710000000000001</v>
+        <v>3.444</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -761,10 +732,10 @@
         <v>46722</v>
       </c>
       <c r="B25">
-        <v>79.162000000000006</v>
+        <v>79.685000000000002</v>
       </c>
       <c r="C25">
-        <v>4.1029999999999998</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -772,10 +743,10 @@
         <v>46753</v>
       </c>
       <c r="B26">
-        <v>78.283000000000001</v>
+        <v>78.888000000000005</v>
       </c>
       <c r="C26">
-        <v>4.5270000000000001</v>
+        <v>4.5110000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -783,10 +754,10 @@
         <v>46784</v>
       </c>
       <c r="B27">
-        <v>77.564999999999998</v>
+        <v>78.233000000000004</v>
       </c>
       <c r="C27">
-        <v>4.1390000000000002</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -794,10 +765,10 @@
         <v>46813</v>
       </c>
       <c r="B28">
-        <v>76.784000000000006</v>
+        <v>77.518000000000001</v>
       </c>
       <c r="C28">
-        <v>3.3650000000000002</v>
+        <v>3.3580000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -805,10 +776,10 @@
         <v>46844</v>
       </c>
       <c r="B29">
-        <v>76.174000000000007</v>
+        <v>76.945999999999998</v>
       </c>
       <c r="C29">
-        <v>3.1509999999999998</v>
+        <v>3.141</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -816,10 +787,10 @@
         <v>46874</v>
       </c>
       <c r="B30">
-        <v>75.611999999999995</v>
+        <v>76.423000000000002</v>
       </c>
       <c r="C30">
-        <v>3.1589999999999998</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -827,10 +798,10 @@
         <v>46905</v>
       </c>
       <c r="B31">
-        <v>74.98</v>
+        <v>75.831999999999994</v>
       </c>
       <c r="C31">
-        <v>3.3140000000000001</v>
+        <v>3.3050000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -838,10 +809,10 @@
         <v>46935</v>
       </c>
       <c r="B32">
-        <v>74.465000000000003</v>
+        <v>75.341999999999999</v>
       </c>
       <c r="C32">
-        <v>3.5209999999999999</v>
+        <v>3.5129999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -849,10 +820,10 @@
         <v>46966</v>
       </c>
       <c r="B33">
-        <v>74</v>
+        <v>74.893000000000001</v>
       </c>
       <c r="C33">
-        <v>3.5779999999999998</v>
+        <v>3.569</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -860,10 +831,10 @@
         <v>46997</v>
       </c>
       <c r="B34">
-        <v>73.533000000000001</v>
+        <v>74.44</v>
       </c>
       <c r="C34">
-        <v>3.55</v>
+        <v>3.5390000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -871,10 +842,10 @@
         <v>47027</v>
       </c>
       <c r="B35">
-        <v>73.135999999999996</v>
+        <v>74.058999999999997</v>
       </c>
       <c r="C35">
-        <v>3.6040000000000001</v>
+        <v>3.5950000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -882,10 +853,10 @@
         <v>47058</v>
       </c>
       <c r="B36">
-        <v>72.727000000000004</v>
+        <v>73.66</v>
       </c>
       <c r="C36">
-        <v>3.8010000000000002</v>
+        <v>3.7970000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -893,10 +864,10 @@
         <v>47088</v>
       </c>
       <c r="B37">
-        <v>72.286000000000001</v>
+        <v>73.23</v>
       </c>
       <c r="C37">
-        <v>4.3719999999999999</v>
+        <v>4.367</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -904,10 +875,10 @@
         <v>47119</v>
       </c>
       <c r="B38">
-        <v>71.856999999999999</v>
+        <v>72.816999999999993</v>
       </c>
       <c r="C38">
-        <v>4.7930000000000001</v>
+        <v>4.7889999999999997</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -915,10 +886,10 @@
         <v>47150</v>
       </c>
       <c r="B39">
-        <v>71.441000000000003</v>
+        <v>72.427000000000007</v>
       </c>
       <c r="C39">
-        <v>4.351</v>
+        <v>4.3470000000000004</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -926,10 +897,10 @@
         <v>47178</v>
       </c>
       <c r="B40">
-        <v>71.037000000000006</v>
+        <v>72.037000000000006</v>
       </c>
       <c r="C40">
-        <v>3.4089999999999998</v>
+        <v>3.4039999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -937,10 +908,10 @@
         <v>47209</v>
       </c>
       <c r="B41">
-        <v>70.676000000000002</v>
+        <v>71.679000000000002</v>
       </c>
       <c r="C41">
-        <v>3.1549999999999998</v>
+        <v>3.1509999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -948,10 +919,10 @@
         <v>47239</v>
       </c>
       <c r="B42">
-        <v>70.275000000000006</v>
+        <v>71.283000000000001</v>
       </c>
       <c r="C42">
-        <v>3.1419999999999999</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -959,10 +930,10 @@
         <v>47270</v>
       </c>
       <c r="B43">
-        <v>69.826999999999998</v>
+        <v>70.834000000000003</v>
       </c>
       <c r="C43">
-        <v>3.2559999999999998</v>
+        <v>3.2519999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -970,10 +941,10 @@
         <v>47300</v>
       </c>
       <c r="B44">
-        <v>69.436999999999998</v>
+        <v>70.456999999999994</v>
       </c>
       <c r="C44">
-        <v>3.452</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -981,10 +952,10 @@
         <v>47331</v>
       </c>
       <c r="B45">
-        <v>69.061000000000007</v>
+        <v>70.087999999999994</v>
       </c>
       <c r="C45">
-        <v>3.5059999999999998</v>
+        <v>3.5019999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -992,10 +963,10 @@
         <v>47362</v>
       </c>
       <c r="B46">
-        <v>68.712999999999994</v>
+        <v>69.753</v>
       </c>
       <c r="C46">
-        <v>3.4969999999999999</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1003,10 +974,10 @@
         <v>47392</v>
       </c>
       <c r="B47">
-        <v>68.367000000000004</v>
+        <v>69.406999999999996</v>
       </c>
       <c r="C47">
-        <v>3.5659999999999998</v>
+        <v>3.5609999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1014,10 +985,10 @@
         <v>47423</v>
       </c>
       <c r="B48">
-        <v>67.95</v>
+        <v>68.989999999999995</v>
       </c>
       <c r="C48">
-        <v>3.7170000000000001</v>
+        <v>3.7120000000000002</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1025,10 +996,10 @@
         <v>47453</v>
       </c>
       <c r="B49">
-        <v>67.584999999999994</v>
+        <v>68.625</v>
       </c>
       <c r="C49">
-        <v>4.2729999999999997</v>
+        <v>4.266</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1036,10 +1007,10 @@
         <v>47484</v>
       </c>
       <c r="B50">
-        <v>67.27</v>
+        <v>68.302999999999997</v>
       </c>
       <c r="C50">
-        <v>4.7300000000000004</v>
+        <v>4.7240000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1047,10 +1018,10 @@
         <v>47515</v>
       </c>
       <c r="B51">
-        <v>66.923000000000002</v>
+        <v>67.936000000000007</v>
       </c>
       <c r="C51">
-        <v>4.32</v>
+        <v>4.3140000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1058,10 +1029,10 @@
         <v>47543</v>
       </c>
       <c r="B52">
-        <v>66.587000000000003</v>
+        <v>67.593000000000004</v>
       </c>
       <c r="C52">
-        <v>3.4769999999999999</v>
+        <v>3.476</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1069,10 +1040,10 @@
         <v>47574</v>
       </c>
       <c r="B53">
-        <v>66.277000000000001</v>
+        <v>67.290999999999997</v>
       </c>
       <c r="C53">
-        <v>3.1379999999999999</v>
+        <v>3.1360000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1080,10 +1051,10 @@
         <v>47604</v>
       </c>
       <c r="B54">
-        <v>65.899000000000001</v>
+        <v>66.893000000000001</v>
       </c>
       <c r="C54">
-        <v>3.1080000000000001</v>
+        <v>3.1040000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1091,10 +1062,10 @@
         <v>47635</v>
       </c>
       <c r="B55">
-        <v>65.539000000000001</v>
+        <v>66.513000000000005</v>
       </c>
       <c r="C55">
-        <v>3.2250000000000001</v>
+        <v>3.2210000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1102,10 +1073,10 @@
         <v>47665</v>
       </c>
       <c r="B56">
-        <v>65.227999999999994</v>
+        <v>66.185000000000002</v>
       </c>
       <c r="C56">
-        <v>3.4620000000000002</v>
+        <v>3.4590000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1113,10 +1084,10 @@
         <v>47696</v>
       </c>
       <c r="B57">
-        <v>64.924999999999997</v>
+        <v>65.870999999999995</v>
       </c>
       <c r="C57">
-        <v>3.5</v>
+        <v>3.4969999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1124,10 +1095,10 @@
         <v>47727</v>
       </c>
       <c r="B58">
-        <v>64.653000000000006</v>
+        <v>65.584000000000003</v>
       </c>
       <c r="C58">
-        <v>3.476</v>
+        <v>3.4729999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1432,1236 +1403,6 @@
   <ignoredErrors>
     <ignoredError sqref="A57:A85 A2:A55 A56" numberStoredAsText="1"/>
   </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FF6D68-A506-45F0-B54E-4A15775B9528}">
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B2">
-        <v>60.07</v>
-      </c>
-      <c r="C2">
-        <v>3.1211000000000002</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>45962</v>
-      </c>
-      <c r="B3">
-        <v>59.478999999999999</v>
-      </c>
-      <c r="C3">
-        <v>3.7837999999999998</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>45992</v>
-      </c>
-      <c r="B4">
-        <v>57.866</v>
-      </c>
-      <c r="C4">
-        <v>4.1501999999999999</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>46023</v>
-      </c>
-      <c r="B5">
-        <v>60.26</v>
-      </c>
-      <c r="C5">
-        <v>7.7126000000000001</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B6">
-        <v>64.522999999999996</v>
-      </c>
-      <c r="C6">
-        <v>3.8382000000000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>46082</v>
-      </c>
-      <c r="B7">
-        <v>90.997</v>
-      </c>
-      <c r="C7">
-        <v>3.0581999999999998</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B8">
-        <v>98.06</v>
-      </c>
-      <c r="C8">
-        <v>2.7736999999999998</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>46143</v>
-      </c>
-      <c r="B9">
-        <v>98.513999999999996</v>
-      </c>
-      <c r="C9">
-        <v>2.8881999999999999</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B10">
-        <v>81.790000000000006</v>
-      </c>
-      <c r="C10">
-        <v>3.1429999999999998</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>46204</v>
-      </c>
-      <c r="B11">
-        <v>79.22</v>
-      </c>
-      <c r="C11">
-        <v>2.9386999999999999</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B12">
-        <v>82.451999999999998</v>
-      </c>
-      <c r="C12">
-        <v>2.7410000000000001</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>46266</v>
-      </c>
-      <c r="B13">
-        <v>95.686999999999998</v>
-      </c>
-      <c r="C13">
-        <v>2.9470000000000001</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
-        <v>46296</v>
-      </c>
-      <c r="B14">
-        <v>95.991</v>
-      </c>
-      <c r="C14">
-        <v>3.0314999999999999</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>46327</v>
-      </c>
-      <c r="B15">
-        <v>98.625</v>
-      </c>
-      <c r="C15">
-        <v>3.1160000000000001</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>46357</v>
-      </c>
-      <c r="B16">
-        <v>96.816000000000003</v>
-      </c>
-      <c r="C16">
-        <v>3.3860000000000001</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>46388</v>
-      </c>
-      <c r="B17">
-        <v>94.762</v>
-      </c>
-      <c r="C17">
-        <v>3.7589999999999999</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>46419</v>
-      </c>
-      <c r="B18">
-        <v>93.150999999999996</v>
-      </c>
-      <c r="C18">
-        <v>3.3860000000000001</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>46447</v>
-      </c>
-      <c r="B19">
-        <v>91.283000000000001</v>
-      </c>
-      <c r="C19">
-        <v>2.6469999999999998</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>46478</v>
-      </c>
-      <c r="B20">
-        <v>89.537000000000006</v>
-      </c>
-      <c r="C20">
-        <v>2.5640000000000001</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>46508</v>
-      </c>
-      <c r="B21">
-        <v>88.12</v>
-      </c>
-      <c r="C21">
-        <v>2.6019999999999999</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
-        <v>46539</v>
-      </c>
-      <c r="B22">
-        <v>86.647000000000006</v>
-      </c>
-      <c r="C22">
-        <v>2.7639999999999998</v>
-      </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>46569</v>
-      </c>
-      <c r="B23">
-        <v>85.049000000000007</v>
-      </c>
-      <c r="C23">
-        <v>3.0049999999999999</v>
-      </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>46600</v>
-      </c>
-      <c r="B24">
-        <v>83.75</v>
-      </c>
-      <c r="C24">
-        <v>3.08</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>46631</v>
-      </c>
-      <c r="B25">
-        <v>82.447000000000003</v>
-      </c>
-      <c r="C25">
-        <v>3.0649999999999999</v>
-      </c>
-      <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>46661</v>
-      </c>
-      <c r="B26">
-        <v>81.272999999999996</v>
-      </c>
-      <c r="C26">
-        <v>3.1520000000000001</v>
-      </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
-        <v>46692</v>
-      </c>
-      <c r="B27">
-        <v>80.242999999999995</v>
-      </c>
-      <c r="C27">
-        <v>3.4710000000000001</v>
-      </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>46722</v>
-      </c>
-      <c r="B28">
-        <v>79.162000000000006</v>
-      </c>
-      <c r="C28">
-        <v>4.1029999999999998</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
-        <v>46753</v>
-      </c>
-      <c r="B29">
-        <v>78.283000000000001</v>
-      </c>
-      <c r="C29">
-        <v>4.5270000000000001</v>
-      </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
-        <v>46784</v>
-      </c>
-      <c r="B30">
-        <v>77.564999999999998</v>
-      </c>
-      <c r="C30">
-        <v>4.1390000000000002</v>
-      </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>46813</v>
-      </c>
-      <c r="B31">
-        <v>76.784000000000006</v>
-      </c>
-      <c r="C31">
-        <v>3.3650000000000002</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>46844</v>
-      </c>
-      <c r="B32">
-        <v>76.174000000000007</v>
-      </c>
-      <c r="C32">
-        <v>3.1509999999999998</v>
-      </c>
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>46874</v>
-      </c>
-      <c r="B33">
-        <v>75.611999999999995</v>
-      </c>
-      <c r="C33">
-        <v>3.1589999999999998</v>
-      </c>
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>46905</v>
-      </c>
-      <c r="B34">
-        <v>74.98</v>
-      </c>
-      <c r="C34">
-        <v>3.3140000000000001</v>
-      </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
-        <v>46935</v>
-      </c>
-      <c r="B35">
-        <v>74.465000000000003</v>
-      </c>
-      <c r="C35">
-        <v>3.5209999999999999</v>
-      </c>
-      <c r="D35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
-        <v>46966</v>
-      </c>
-      <c r="B36">
-        <v>74</v>
-      </c>
-      <c r="C36">
-        <v>3.5779999999999998</v>
-      </c>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
-        <v>46997</v>
-      </c>
-      <c r="B37">
-        <v>73.533000000000001</v>
-      </c>
-      <c r="C37">
-        <v>3.55</v>
-      </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
-        <v>47027</v>
-      </c>
-      <c r="B38">
-        <v>73.135999999999996</v>
-      </c>
-      <c r="C38">
-        <v>3.6040000000000001</v>
-      </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
-        <v>47058</v>
-      </c>
-      <c r="B39">
-        <v>72.727000000000004</v>
-      </c>
-      <c r="C39">
-        <v>3.8010000000000002</v>
-      </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
-        <v>47088</v>
-      </c>
-      <c r="B40">
-        <v>72.286000000000001</v>
-      </c>
-      <c r="C40">
-        <v>4.3719999999999999</v>
-      </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>47119</v>
-      </c>
-      <c r="B41">
-        <v>71.856999999999999</v>
-      </c>
-      <c r="C41">
-        <v>4.7930000000000001</v>
-      </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
-        <v>47150</v>
-      </c>
-      <c r="B42">
-        <v>71.441000000000003</v>
-      </c>
-      <c r="C42">
-        <v>4.351</v>
-      </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
-        <v>47178</v>
-      </c>
-      <c r="B43">
-        <v>71.037000000000006</v>
-      </c>
-      <c r="C43">
-        <v>3.4089999999999998</v>
-      </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>47209</v>
-      </c>
-      <c r="B44">
-        <v>70.676000000000002</v>
-      </c>
-      <c r="C44">
-        <v>3.1549999999999998</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
-        <v>47239</v>
-      </c>
-      <c r="B45">
-        <v>70.275000000000006</v>
-      </c>
-      <c r="C45">
-        <v>3.1419999999999999</v>
-      </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
-        <v>47270</v>
-      </c>
-      <c r="B46">
-        <v>69.826999999999998</v>
-      </c>
-      <c r="C46">
-        <v>3.2559999999999998</v>
-      </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>47300</v>
-      </c>
-      <c r="B47">
-        <v>69.436999999999998</v>
-      </c>
-      <c r="C47">
-        <v>3.452</v>
-      </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
-        <v>47331</v>
-      </c>
-      <c r="B48">
-        <v>69.061000000000007</v>
-      </c>
-      <c r="C48">
-        <v>3.5059999999999998</v>
-      </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
-        <v>47362</v>
-      </c>
-      <c r="B49">
-        <v>68.712999999999994</v>
-      </c>
-      <c r="C49">
-        <v>3.4969999999999999</v>
-      </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
-        <v>47392</v>
-      </c>
-      <c r="B50">
-        <v>68.367000000000004</v>
-      </c>
-      <c r="C50">
-        <v>3.5659999999999998</v>
-      </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
-        <v>47423</v>
-      </c>
-      <c r="B51">
-        <v>67.95</v>
-      </c>
-      <c r="C51">
-        <v>3.7170000000000001</v>
-      </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>47453</v>
-      </c>
-      <c r="B52">
-        <v>67.584999999999994</v>
-      </c>
-      <c r="C52">
-        <v>4.2729999999999997</v>
-      </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
-        <v>47484</v>
-      </c>
-      <c r="B53">
-        <v>67.27</v>
-      </c>
-      <c r="C53">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
-        <v>47515</v>
-      </c>
-      <c r="B54">
-        <v>66.923000000000002</v>
-      </c>
-      <c r="C54">
-        <v>4.32</v>
-      </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
-        <v>47543</v>
-      </c>
-      <c r="B55">
-        <v>66.587000000000003</v>
-      </c>
-      <c r="C55">
-        <v>3.4769999999999999</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>47574</v>
-      </c>
-      <c r="B56">
-        <v>66.277000000000001</v>
-      </c>
-      <c r="C56">
-        <v>3.1379999999999999</v>
-      </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>47604</v>
-      </c>
-      <c r="B57">
-        <v>65.899000000000001</v>
-      </c>
-      <c r="C57">
-        <v>3.1080000000000001</v>
-      </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
-        <v>47635</v>
-      </c>
-      <c r="B58">
-        <v>65.539000000000001</v>
-      </c>
-      <c r="C58">
-        <v>3.2250000000000001</v>
-      </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
-        <v>47665</v>
-      </c>
-      <c r="B59">
-        <v>65.227999999999994</v>
-      </c>
-      <c r="C59">
-        <v>3.4620000000000002</v>
-      </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>47696</v>
-      </c>
-      <c r="B60">
-        <v>64.924999999999997</v>
-      </c>
-      <c r="C60">
-        <v>3.5</v>
-      </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="6">
-        <v>47727</v>
-      </c>
-      <c r="B61">
-        <v>64.653000000000006</v>
-      </c>
-      <c r="C61">
-        <v>3.476</v>
-      </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="6">
-        <v>46311</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2699,6 +1440,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -2993,15 +1743,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F143CCCD-40B6-4B8D-A7F2-4E615A6C1F5F}">
   <ds:schemaRefs>
@@ -3014,6 +1755,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1D49D99-C5F7-40FC-8E67-9119B00EF26A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3030,12 +1779,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBFD1C9B-7037-417F-8C82-28A90281D10E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>